--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_42.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3270873.715260589</v>
+        <v>3271989.526823967</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13636053.96684475</v>
+        <v>13618430.38276779</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13636053.96684475</v>
+        <v>13618430.38276779</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143186.9484571627</v>
+        <v>134701.7887430227</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143186.9484571627</v>
+        <v>134701.7887430227</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25064204.86404417</v>
+        <v>25063199.68321406</v>
       </c>
     </row>
   </sheetData>
@@ -672,10 +672,10 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.769060713576095</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.953406460793027</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.36594612241274</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
         <v>184.8629887637397</v>
@@ -739,13 +739,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.464774651476091</v>
+        <v>13.26666376145554</v>
       </c>
       <c r="U3" t="n">
         <v>0.1957842884886531</v>
@@ -796,13 +796,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>133.7852422200173</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>374.0000000000005</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>374.0000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.343301935257416</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.72246717437136</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.41253966161939</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8629887637398</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.18817092047</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>144.6926477280658</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1018,22 +1018,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>316.2496320402737</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>374.0000000000006</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.46477465147608</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886345</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>374.0000000000006</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.51638189435316</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
         <v>142.7621408454554</v>
@@ -1091,7 +1091,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>264.9837661807365</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
         <v>310.286266425598</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935258406</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
         <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.953406460792545</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>317.110228669769</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
         <v>133.5184388018132</v>
@@ -1261,7 +1261,7 @@
         <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>112.2367059703185</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
         <v>0.1957842884886531</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>374.0000000000006</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374.0000000000006</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1383,7 +1383,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H11" t="n">
-        <v>72.59985970855254</v>
+        <v>70.10795863165528</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.388898923102697</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T11" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U11" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1453,19 +1453,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.986705686348098</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H12" t="n">
-        <v>324.89733246944</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,28 +1489,28 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.532287858417</v>
+        <v>181.0524309641363</v>
       </c>
       <c r="S12" t="n">
-        <v>247.3260751919546</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T12" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M13" t="n">
         <v>100.6963655009106</v>
@@ -1574,7 +1574,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S13" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>72.59985970855251</v>
       </c>
       <c r="I14" t="n">
-        <v>1.388898923102767</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>328.1087337345404</v>
       </c>
       <c r="V14" t="n">
-        <v>308.8510241668239</v>
+        <v>306.3591230899268</v>
       </c>
       <c r="W14" t="n">
         <v>317.3734759809475</v>
@@ -1687,22 +1687,22 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>196.7134233626612</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H15" t="n">
-        <v>324.89733246944</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S15" t="n">
-        <v>131.5805093985736</v>
+        <v>133.100652504293</v>
       </c>
       <c r="T15" t="n">
         <v>81.32333125524968</v>
@@ -1857,10 +1857,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H17" t="n">
-        <v>72.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I17" t="n">
-        <v>1.388898923102767</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>141.7853537319712</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T17" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U17" t="n">
-        <v>328.1087337345404</v>
+        <v>325.6168326576429</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1924,19 +1924,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>214.3988148982253</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H18" t="n">
-        <v>3.897332469440016</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T18" t="n">
-        <v>81.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
@@ -1987,7 +1987,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>271.1181104424475</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8.713201928270962</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M19" t="n">
         <v>100.6963655009106</v>
@@ -2048,7 +2048,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S19" t="n">
-        <v>30.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>128.4745782429939</v>
+        <v>125.9826771660967</v>
       </c>
       <c r="D20" t="n">
         <v>89.33915573984979</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.388898923102697</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>141.7853537319712</v>
@@ -2161,13 +2161,13 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
         <v>3.986705686348103</v>
@@ -2212,16 +2212,16 @@
         <v>81.32333125524968</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16083145829998</v>
+        <v>271.8875491346129</v>
       </c>
       <c r="V21" t="n">
-        <v>286.2373848678333</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>78.39139276613435</v>
@@ -2331,10 +2331,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H23" t="n">
-        <v>72.59985970855251</v>
+        <v>70.10795863167058</v>
       </c>
       <c r="I23" t="n">
-        <v>1.388898923102767</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-6.516676633069503e-13</v>
       </c>
       <c r="S23" t="n">
         <v>141.7853537319712</v>
@@ -2401,13 +2401,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>119.7322714797289</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H24" t="n">
         <v>3.897332469440016</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>179.532287858417</v>
@@ -2455,13 +2455,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>304.0998605861413</v>
       </c>
       <c r="X24" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.35033711113681</v>
+        <v>78.85843603423959</v>
       </c>
       <c r="H26" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,16 +2598,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.388898923100896</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T26" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2638,16 +2638,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9867056863481</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H27" t="n">
-        <v>119.6428982628204</v>
+        <v>196.6240501457527</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>179.532287858417</v>
@@ -2683,22 +2683,22 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T27" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M28" t="n">
         <v>100.6963655009106</v>
@@ -2759,7 +2759,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S28" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>143.174252655072</v>
+        <v>139.2934526550737</v>
       </c>
       <c r="T29" t="n">
         <v>259.5162852461518</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>256.2832743226395</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
@@ -2884,7 +2884,7 @@
         <v>3.986705686348098</v>
       </c>
       <c r="H30" t="n">
-        <v>3.897332469439999</v>
+        <v>119.6428982628209</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,13 +2911,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R30" t="n">
         <v>179.532287858417</v>
       </c>
       <c r="S30" t="n">
-        <v>131.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T30" t="n">
         <v>81.32333125524967</v>
@@ -2932,7 +2932,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -3042,7 +3042,7 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H32" t="n">
-        <v>72.59985970855254</v>
+        <v>70.10795863165528</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.388898923100896</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T32" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3109,7 +3109,7 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>21.67209722191262</v>
@@ -3118,10 +3118,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H33" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>179.532287858417</v>
@@ -3157,10 +3157,10 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T33" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1608314583</v>
+        <v>271.8875491346126</v>
       </c>
       <c r="V33" t="n">
         <v>414.5106671915202</v>
@@ -3169,7 +3169,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>214.6083052387681</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M34" t="n">
         <v>100.6963655009106</v>
@@ -3233,7 +3233,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S34" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,10 +3276,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>57.35033711113682</v>
+        <v>57.35033711113681</v>
       </c>
       <c r="H35" t="n">
-        <v>48.59985970855254</v>
+        <v>48.59985970855251</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,16 +3309,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>7.520898923102522</v>
       </c>
       <c r="S35" t="n">
-        <v>117.7853537319711</v>
+        <v>117.7853537319712</v>
       </c>
       <c r="T35" t="n">
         <v>235.5162852461518</v>
       </c>
       <c r="U35" t="n">
-        <v>304.1087337345403</v>
+        <v>304.1087337345404</v>
       </c>
       <c r="V35" t="n">
         <v>284.8510241668239</v>
@@ -3330,7 +3330,7 @@
         <v>247.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>154.4343316059687</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>39.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>35.86185704354964</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9867056863481</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3394,10 +3394,10 @@
         <v>107.5805093985736</v>
       </c>
       <c r="T36" t="n">
-        <v>57.32333125524966</v>
+        <v>57.32333125524968</v>
       </c>
       <c r="U36" t="n">
-        <v>55.16083145829995</v>
+        <v>68.42667774534588</v>
       </c>
       <c r="V36" t="n">
         <v>69.51066719152016</v>
@@ -3409,7 +3409,7 @@
         <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>76.69636550091056</v>
+        <v>76.69636550091059</v>
       </c>
       <c r="N37" t="n">
         <v>129.602288386439</v>
@@ -3470,7 +3470,7 @@
         <v>353.2234394565609</v>
       </c>
       <c r="S37" t="n">
-        <v>6.374299374986586</v>
+        <v>6.374299374986606</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>48.59985970855254</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>7.520898923102804</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>105.9022526551334</v>
+        <v>117.7853537319711</v>
       </c>
       <c r="T38" t="n">
         <v>235.5162852461518</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39.55655664632658</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
@@ -3622,13 +3622,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.72980216731037</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R39" t="n">
         <v>155.532287858417</v>
       </c>
       <c r="S39" t="n">
-        <v>107.5805093985736</v>
+        <v>126.2101133477429</v>
       </c>
       <c r="T39" t="n">
         <v>57.32333125524966</v>
@@ -3741,16 +3741,16 @@
         <v>128.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>89.33915573984979</v>
+        <v>9.46331008897012</v>
       </c>
       <c r="E41" t="n">
-        <v>83.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>83.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>61.57596976883968</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>72.59985970855254</v>
@@ -3792,7 +3792,7 @@
         <v>259.5162852461518</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V41" t="n">
         <v>308.8510241668239</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
@@ -3826,13 +3826,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9867056863481</v>
+        <v>119.7322714797289</v>
       </c>
       <c r="H42" t="n">
-        <v>324.89733246944</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3871,10 +3871,10 @@
         <v>81.32333125524967</v>
       </c>
       <c r="U42" t="n">
-        <v>176.025443586883</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V42" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
         <v>111.3731429098285</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>141.2249456132775</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>128.4745782429939</v>
@@ -4026,13 +4026,13 @@
         <v>141.7853537319712</v>
       </c>
       <c r="T44" t="n">
-        <v>259.5162852461518</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V44" t="n">
-        <v>308.8510241668239</v>
+        <v>239.8882083360786</v>
       </c>
       <c r="W44" t="n">
         <v>317.3734759809475</v>
@@ -4057,19 +4057,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>123.8022990262926</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>137.4176630152935</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
         <v>3.986705686348103</v>
       </c>
       <c r="H45" t="n">
-        <v>3.897332469440016</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>79.16083145829998</v>
       </c>
       <c r="V45" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>432.3731429098285</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C2" t="n">
-        <v>56.89417848844994</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D2" t="n">
-        <v>46.45058683203604</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E2" t="n">
-        <v>42.04322359277478</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F2" t="n">
-        <v>37.1042046957931</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G2" t="n">
-        <v>33.7271320339169</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92000000000004</v>
+        <v>31.89313783918488</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>209.721232153843</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>261.8658206463053</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L2" t="n">
-        <v>326.5557936111294</v>
+        <v>326.5557936111288</v>
       </c>
       <c r="M2" t="n">
-        <v>696.8157936111299</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.07579361113</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.07579361113</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.740000000002</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496.000000000002</v>
+        <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496.000000000002</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.751569573323</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3160547407874</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1433030571269</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>496.3620141874828</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1379399847881</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.6960887900342</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.534702729969</v>
+        <v>1070.772466608729</v>
       </c>
       <c r="C3" t="n">
-        <v>241.534702729969</v>
+        <v>1070.772466608729</v>
       </c>
       <c r="D3" t="n">
-        <v>241.534702729969</v>
+        <v>719.3202576211509</v>
       </c>
       <c r="E3" t="n">
-        <v>241.534702729969</v>
+        <v>373.1868260838654</v>
       </c>
       <c r="F3" t="n">
-        <v>241.534702729969</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="G3" t="n">
-        <v>241.534702729969</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="H3" t="n">
-        <v>241.534702729969</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92000000000004</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>174.5985557413368</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>399.2086311753428</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>718.1819687139391</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>859.8361604567983</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1050.16096421531</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.388006370727</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1495.800085368536</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.538506374912</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.671396474091</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.591741468861</v>
+        <v>1151.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1147.081868083532</v>
+        <v>1138.390985634209</v>
       </c>
       <c r="U3" t="n">
-        <v>1146.884106175968</v>
+        <v>1138.193223726645</v>
       </c>
       <c r="V3" t="n">
-        <v>1132.226866588574</v>
+        <v>1123.535984139251</v>
       </c>
       <c r="W3" t="n">
-        <v>997.0902582855258</v>
+        <v>1090.835839785888</v>
       </c>
       <c r="X3" t="n">
-        <v>619.3124805077474</v>
+        <v>1070.772466608729</v>
       </c>
       <c r="Y3" t="n">
-        <v>241.534702729969</v>
+        <v>1070.772466608729</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1114.67878247329</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="C4" t="n">
-        <v>1240.680788291726</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="D4" t="n">
-        <v>1353.999932416726</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="E4" t="n">
-        <v>1353.999932416726</v>
+        <v>377.0650415791451</v>
       </c>
       <c r="F4" t="n">
-        <v>1353.999932416726</v>
+        <v>377.0650415791451</v>
       </c>
       <c r="G4" t="n">
-        <v>1353.999932416726</v>
+        <v>481.6391623681918</v>
       </c>
       <c r="H4" t="n">
-        <v>1353.999932416726</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="I4" t="n">
-        <v>1496.000000000002</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J4" t="n">
-        <v>1496.000000000002</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1496.000000000002</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1496.000000000002</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.559210207726</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1259.355027535549</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.999084352573</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>775.3387144730414</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>461.9182433360737</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>140.4529045904168</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>180.9076923075407</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>369.7690419581489</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>369.7690419581489</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="V4" t="n">
-        <v>568.5904348440948</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="W4" t="n">
-        <v>740.4813531037722</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="X4" t="n">
-        <v>891.5121441279657</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="Y4" t="n">
-        <v>1002.921444806998</v>
+        <v>259.2361373677321</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.8416377852051</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.86731632763546</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>48.42372467122154</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>44.01636143196028</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>39.07734253497861</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310243</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.1800000000006</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4400000000013</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>835.1299729648254</v>
+        <v>770.5396902997726</v>
       </c>
       <c r="M5" t="n">
-        <v>835.1299729648254</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.07579361113</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.07579361113</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.740000000002</v>
+        <v>1199.463896688644</v>
       </c>
       <c r="Q5" t="n">
-        <v>1496.000000000002</v>
+        <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1496.000000000002</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.724707412508</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.994415731963</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.2891925799729</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.1164408963124</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.3351520266684</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.1110778239737</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.6692266292197</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,31 +4613,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>381.3722089875785</v>
+        <v>847.9471502738977</v>
       </c>
       <c r="C6" t="n">
-        <v>381.3722089875785</v>
+        <v>847.9471502738977</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92000000000004</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92000000000004</v>
+        <v>701.7929606495888</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92000000000004</v>
+        <v>358.7260491971879</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.5985557413368</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
         <v>399.2086311753428</v>
@@ -4661,28 +4661,28 @@
         <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1176.356012600582</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>798.5782348228038</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>794.0683614374744</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>793.8705995299101</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>779.213359942516</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W6" t="n">
-        <v>401.4355821647376</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X6" t="n">
-        <v>381.3722089875785</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y6" t="n">
-        <v>381.3722089875785</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="7">
@@ -4692,25 +4692,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>750.3656224480467</v>
+        <v>576.0083476291953</v>
       </c>
       <c r="C7" t="n">
-        <v>876.3676282664825</v>
+        <v>702.0103534476311</v>
       </c>
       <c r="D7" t="n">
-        <v>989.6867723914826</v>
+        <v>815.3294975726312</v>
       </c>
       <c r="E7" t="n">
-        <v>1107.515676602896</v>
+        <v>933.1584017840443</v>
       </c>
       <c r="F7" t="n">
-        <v>1231.876649194831</v>
+        <v>1057.51937437598</v>
       </c>
       <c r="G7" t="n">
-        <v>1385.467095409585</v>
+        <v>1211.109820590734</v>
       </c>
       <c r="H7" t="n">
-        <v>1385.467095409585</v>
+        <v>1382.26126902882</v>
       </c>
       <c r="I7" t="n">
         <v>1385.467095409585</v>
@@ -4737,31 +4737,31 @@
         <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.3853387456569</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.37478771712398</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7973598420843</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>527.1989841027222</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>527.1989841027222</v>
+        <v>201.8109182596774</v>
       </c>
       <c r="X7" t="n">
-        <v>527.1989841027222</v>
+        <v>352.841709283871</v>
       </c>
       <c r="Y7" t="n">
-        <v>638.6082847817545</v>
+        <v>464.2510099629032</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.8416377852049</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>58.86731632763531</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>48.42372467122141</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>44.01636143196015</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>39.07734253497847</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>35.70026987310129</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>31.89313783918443</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977268</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>82.164278792235</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>146.8542517570591</v>
+        <v>835.1299729648241</v>
       </c>
       <c r="M8" t="n">
-        <v>517.1142517570597</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>887.3742517570603</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.07579361113</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.740000000002</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1496.000000000002</v>
+        <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496.000000000002</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.724707412508</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.994415731963</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>971.2891925799728</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>739.1164408963123</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>498.3351520266682</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>304.1110778239735</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.6692266292196</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4856,25 +4856,25 @@
         <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5985557413368</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
         <v>399.2086311753428</v>
@@ -4883,7 +4883,7 @@
         <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>859.8361604567981</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
         <v>1050.16096421531</v>
@@ -4895,31 +4895,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495.800085368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1360.932975467714</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S9" t="n">
-        <v>1297.853320462485</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T9" t="n">
-        <v>1184.482910391456</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U9" t="n">
-        <v>1184.285148483892</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V9" t="n">
-        <v>1169.627908896498</v>
+        <v>1132.226866588574</v>
       </c>
       <c r="W9" t="n">
-        <v>1136.927764543135</v>
+        <v>1099.526722235211</v>
       </c>
       <c r="X9" t="n">
-        <v>759.1499867653569</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="Y9" t="n">
-        <v>381.3722089875785</v>
+        <v>701.6855712802744</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>444.5722170866418</v>
+        <v>638.3121162551106</v>
       </c>
       <c r="C10" t="n">
-        <v>570.5742229050776</v>
+        <v>638.3121162551106</v>
       </c>
       <c r="D10" t="n">
-        <v>577.9735815213666</v>
+        <v>751.6312603801107</v>
       </c>
       <c r="E10" t="n">
-        <v>577.9735815213666</v>
+        <v>869.4601645915237</v>
       </c>
       <c r="F10" t="n">
-        <v>702.334554113302</v>
+        <v>869.4601645915237</v>
       </c>
       <c r="G10" t="n">
-        <v>855.9250003280562</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="H10" t="n">
-        <v>1027.076448766142</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I10" t="n">
-        <v>1253.739110653045</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J10" t="n">
-        <v>1253.739110653045</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
         <v>1385.467095409585</v>
@@ -4974,31 +4974,31 @@
         <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3853387456569</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
-        <v>29.92000000000004</v>
+        <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.37478771712395</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>70.37478771712395</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U10" t="n">
-        <v>70.37478771712395</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="V10" t="n">
-        <v>70.37478771712395</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="W10" t="n">
-        <v>70.37478771712395</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="X10" t="n">
-        <v>221.4055787413175</v>
+        <v>467.9668012156696</v>
       </c>
       <c r="Y10" t="n">
-        <v>332.8148794203497</v>
+        <v>526.5547785888184</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045681</v>
       </c>
       <c r="D11" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501743</v>
       </c>
       <c r="E11" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129333</v>
       </c>
       <c r="F11" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179718</v>
       </c>
       <c r="G11" t="n">
-        <v>125.2531916248006</v>
+        <v>122.6561198299548</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J11" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K11" t="n">
-        <v>777.9635720585666</v>
+        <v>776.8935720585665</v>
       </c>
       <c r="L11" t="n">
-        <v>1420.473572058567</v>
+        <v>1418.413572058566</v>
       </c>
       <c r="M11" t="n">
-        <v>1588.310595394003</v>
+        <v>2059.933572058567</v>
       </c>
       <c r="N11" t="n">
-        <v>2230.820595394003</v>
+        <v>2226.820595394003</v>
       </c>
       <c r="O11" t="n">
-        <v>2395.974106525702</v>
+        <v>2391.974106525702</v>
       </c>
       <c r="P11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R11" t="n">
-        <v>2594.597071794846</v>
+        <v>2592</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X11" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.041188948283</v>
+        <v>685.6142945751448</v>
       </c>
       <c r="C12" t="n">
-        <v>1100.536226882101</v>
+        <v>645.1093325089637</v>
       </c>
       <c r="D12" t="n">
-        <v>1073.326442136947</v>
+        <v>617.8995477638096</v>
       </c>
       <c r="E12" t="n">
-        <v>727.1930105996616</v>
+        <v>596.0085404689484</v>
       </c>
       <c r="F12" t="n">
-        <v>384.1260991472608</v>
+        <v>577.1840532589717</v>
       </c>
       <c r="G12" t="n">
-        <v>380.0991237065051</v>
+        <v>248.9146535757918</v>
       </c>
       <c r="H12" t="n">
-        <v>51.92</v>
+        <v>244.9779541117109</v>
       </c>
       <c r="I12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J12" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K12" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L12" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M12" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N12" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O12" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P12" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2184.512931092847</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2003.167185781314</v>
+        <v>2079.310426970418</v>
       </c>
       <c r="S12" t="n">
-        <v>1753.342867405603</v>
+        <v>1946.400821517313</v>
       </c>
       <c r="T12" t="n">
-        <v>1671.198088359896</v>
+        <v>1864.256042471607</v>
       </c>
       <c r="U12" t="n">
-        <v>1591.237652543431</v>
+        <v>1784.295606655142</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.782433158057</v>
+        <v>1689.840387269768</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.284309006715</v>
+        <v>1253.099838876002</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.422956031576</v>
+        <v>828.9960616584386</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.239731015279</v>
+        <v>749.8128366421413</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>675.5869414962938</v>
+        <v>675.5069414962938</v>
       </c>
       <c r="C13" t="n">
-        <v>723.3789473147295</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D13" t="n">
-        <v>758.4880914397296</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E13" t="n">
-        <v>798.1069956511426</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F13" t="n">
-        <v>844.257968243078</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G13" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H13" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I13" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J13" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K13" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L13" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M13" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N13" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O13" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P13" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.6348877086339</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R13" t="n">
-        <v>82.60111047978444</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S13" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T13" t="n">
-        <v>153.3519263756527</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U13" t="n">
-        <v>321.7272009811524</v>
+        <v>321.6472009811525</v>
       </c>
       <c r="V13" t="n">
-        <v>442.3385938670984</v>
+        <v>442.2585938670985</v>
       </c>
       <c r="W13" t="n">
-        <v>536.0195121267758</v>
+        <v>535.9395121267759</v>
       </c>
       <c r="X13" t="n">
-        <v>608.8403031509694</v>
+        <v>608.7603031509694</v>
       </c>
       <c r="Y13" t="n">
-        <v>642.0396038300016</v>
+        <v>641.9596038300017</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.7843919601175</v>
+        <v>596.3014637549632</v>
       </c>
       <c r="C14" t="n">
-        <v>468.0120907045681</v>
+        <v>466.5291624994138</v>
       </c>
       <c r="D14" t="n">
-        <v>377.7705192501743</v>
+        <v>376.28759104502</v>
       </c>
       <c r="E14" t="n">
-        <v>293.5651762129333</v>
+        <v>292.082248007779</v>
       </c>
       <c r="F14" t="n">
-        <v>208.8281775179718</v>
+        <v>207.3452493128175</v>
       </c>
       <c r="G14" t="n">
-        <v>126.6561198299548</v>
+        <v>125.1731916248005</v>
       </c>
       <c r="H14" t="n">
-        <v>53.32292820515431</v>
+        <v>51.84</v>
       </c>
       <c r="I14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J14" t="n">
-        <v>561.4552612788618</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K14" t="n">
-        <v>738.645610525093</v>
+        <v>776.8935720585665</v>
       </c>
       <c r="L14" t="n">
-        <v>958.4659070075052</v>
+        <v>996.7138685409786</v>
       </c>
       <c r="M14" t="n">
-        <v>999.286970190582</v>
+        <v>1638.23386854098</v>
       </c>
       <c r="N14" t="n">
-        <v>1641.796970190582</v>
+        <v>2226.820595394003</v>
       </c>
       <c r="O14" t="n">
-        <v>1806.950481322281</v>
+        <v>2391.974106525702</v>
       </c>
       <c r="P14" t="n">
-        <v>2006.976374796579</v>
+        <v>2592</v>
       </c>
       <c r="Q14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S14" t="n">
-        <v>2452.782470977807</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T14" t="n">
-        <v>2190.644809113007</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U14" t="n">
-        <v>1859.221845744784</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V14" t="n">
-        <v>1547.251114263144</v>
+        <v>1545.76818605799</v>
       </c>
       <c r="W14" t="n">
-        <v>1226.67184559552</v>
+        <v>1225.188917390366</v>
       </c>
       <c r="X14" t="n">
-        <v>952.6497915948457</v>
+        <v>951.1668633896913</v>
       </c>
       <c r="Y14" t="n">
-        <v>760.4099606021121</v>
+        <v>758.9270323969577</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1335.714641146579</v>
+        <v>1009.856718817569</v>
       </c>
       <c r="C15" t="n">
-        <v>1295.209679080397</v>
+        <v>969.3517567513879</v>
       </c>
       <c r="D15" t="n">
-        <v>943.7574700928189</v>
+        <v>942.1419720062338</v>
       </c>
       <c r="E15" t="n">
-        <v>921.8664627979578</v>
+        <v>596.0085404689484</v>
       </c>
       <c r="F15" t="n">
-        <v>578.7995513455569</v>
+        <v>252.9416290165474</v>
       </c>
       <c r="G15" t="n">
-        <v>380.0991237065051</v>
+        <v>248.9146535757918</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>244.9779541117109</v>
       </c>
       <c r="I15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J15" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K15" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L15" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M15" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N15" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P15" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2080.925925057003</v>
+        <v>1756.603500814579</v>
       </c>
       <c r="S15" t="n">
-        <v>1948.016319603899</v>
+        <v>1622.158397274889</v>
       </c>
       <c r="T15" t="n">
-        <v>1865.871540558192</v>
+        <v>1540.013618229182</v>
       </c>
       <c r="U15" t="n">
-        <v>1785.911104741727</v>
+        <v>1460.053182412718</v>
       </c>
       <c r="V15" t="n">
-        <v>1691.455885356353</v>
+        <v>1365.597963027344</v>
       </c>
       <c r="W15" t="n">
-        <v>1578.957761205011</v>
+        <v>1253.099838876002</v>
       </c>
       <c r="X15" t="n">
-        <v>1479.096408229872</v>
+        <v>1153.238485900863</v>
       </c>
       <c r="Y15" t="n">
-        <v>1399.913183213575</v>
+        <v>1074.055260884566</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>675.5869414962938</v>
+        <v>675.5069414962938</v>
       </c>
       <c r="C16" t="n">
-        <v>723.3789473147295</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D16" t="n">
-        <v>758.4880914397296</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E16" t="n">
-        <v>798.1069956511426</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F16" t="n">
-        <v>844.257968243078</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G16" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H16" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I16" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J16" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K16" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L16" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M16" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N16" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O16" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P16" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R16" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S16" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T16" t="n">
-        <v>164.4554332571655</v>
+        <v>153.2719263756527</v>
       </c>
       <c r="U16" t="n">
-        <v>332.8307078626652</v>
+        <v>321.6472009811525</v>
       </c>
       <c r="V16" t="n">
-        <v>453.4421007486112</v>
+        <v>442.2585938670985</v>
       </c>
       <c r="W16" t="n">
-        <v>547.1230190082886</v>
+        <v>535.9395121267759</v>
       </c>
       <c r="X16" t="n">
-        <v>608.8403031509694</v>
+        <v>608.7603031509694</v>
       </c>
       <c r="Y16" t="n">
-        <v>642.0396038300016</v>
+        <v>641.9596038300017</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.7843919601175</v>
+        <v>596.3014637549633</v>
       </c>
       <c r="C17" t="n">
-        <v>468.0120907045681</v>
+        <v>466.5291624994138</v>
       </c>
       <c r="D17" t="n">
-        <v>377.7705192501743</v>
+        <v>376.2875910450201</v>
       </c>
       <c r="E17" t="n">
-        <v>293.5651762129333</v>
+        <v>292.082248007779</v>
       </c>
       <c r="F17" t="n">
-        <v>208.8281775179718</v>
+        <v>207.3452493128175</v>
       </c>
       <c r="G17" t="n">
-        <v>126.6561198299548</v>
+        <v>125.1731916248006</v>
       </c>
       <c r="H17" t="n">
-        <v>53.32292820515431</v>
+        <v>51.84</v>
       </c>
       <c r="I17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J17" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K17" t="n">
-        <v>312.6439213047977</v>
+        <v>312.5639213047978</v>
       </c>
       <c r="L17" t="n">
-        <v>532.4642177872098</v>
+        <v>532.3842177872099</v>
       </c>
       <c r="M17" t="n">
-        <v>1174.97421778721</v>
+        <v>1173.904217787211</v>
       </c>
       <c r="N17" t="n">
-        <v>1641.796970190582</v>
+        <v>1308.959999999997</v>
       </c>
       <c r="O17" t="n">
-        <v>1806.950481322281</v>
+        <v>1950.479999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>2006.976374796579</v>
+        <v>2592</v>
       </c>
       <c r="Q17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.782470977807</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T17" t="n">
-        <v>2190.644809113007</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U17" t="n">
-        <v>1859.221845744784</v>
+        <v>1857.73891753963</v>
       </c>
       <c r="V17" t="n">
-        <v>1547.251114263144</v>
+        <v>1545.76818605799</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.67184559552</v>
+        <v>1225.188917390366</v>
       </c>
       <c r="X17" t="n">
-        <v>952.6497915948457</v>
+        <v>951.1668633896916</v>
       </c>
       <c r="Y17" t="n">
-        <v>760.4099606021121</v>
+        <v>758.9270323969578</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>816.7987647058582</v>
+        <v>1011.392216904154</v>
       </c>
       <c r="C18" t="n">
-        <v>452.0513783972528</v>
+        <v>646.6448305955485</v>
       </c>
       <c r="D18" t="n">
-        <v>424.8415936520986</v>
+        <v>295.19262160797</v>
       </c>
       <c r="E18" t="n">
-        <v>78.70816211481312</v>
+        <v>78.62816211481311</v>
       </c>
       <c r="F18" t="n">
-        <v>59.88367490483648</v>
+        <v>59.80367490483647</v>
       </c>
       <c r="G18" t="n">
-        <v>55.85669946408083</v>
+        <v>55.77669946408081</v>
       </c>
       <c r="H18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J18" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K18" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L18" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M18" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N18" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O18" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P18" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2080.925925057003</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S18" t="n">
-        <v>1948.016319603899</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T18" t="n">
-        <v>1865.871540558192</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U18" t="n">
-        <v>1785.911104741727</v>
+        <v>1785.831104741727</v>
       </c>
       <c r="V18" t="n">
-        <v>1691.455885356353</v>
+        <v>1691.375885356353</v>
       </c>
       <c r="W18" t="n">
-        <v>1578.957761205011</v>
+        <v>1578.877761205011</v>
       </c>
       <c r="X18" t="n">
-        <v>1479.096408229872</v>
+        <v>1479.016408229872</v>
       </c>
       <c r="Y18" t="n">
-        <v>1205.239731015279</v>
+        <v>1399.833183213575</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C19" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4024541962424</v>
       </c>
       <c r="D19" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5115983212424</v>
       </c>
       <c r="E19" t="n">
-        <v>798.1069956511426</v>
+        <v>809.1305025326554</v>
       </c>
       <c r="F19" t="n">
-        <v>844.257968243078</v>
+        <v>855.2814751245909</v>
       </c>
       <c r="G19" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1028770770499</v>
       </c>
       <c r="H19" t="n">
-        <v>1016.941316010672</v>
+        <v>1027.964822892185</v>
       </c>
       <c r="I19" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.678226418432</v>
       </c>
       <c r="J19" t="n">
-        <v>1505.704370025436</v>
+        <v>1516.727876906949</v>
       </c>
       <c r="K19" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L19" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057278</v>
       </c>
       <c r="M19" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N19" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O19" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P19" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R19" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978443</v>
       </c>
       <c r="S19" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T19" t="n">
-        <v>153.3519263756527</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U19" t="n">
-        <v>321.7272009811524</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V19" t="n">
-        <v>442.3385938670984</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W19" t="n">
-        <v>536.0195121267758</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X19" t="n">
-        <v>608.8403031509694</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y19" t="n">
-        <v>642.0396038300016</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C20" t="n">
-        <v>466.6091624994138</v>
+        <v>466.5291624994138</v>
       </c>
       <c r="D20" t="n">
-        <v>376.36759104502</v>
+        <v>376.28759104502</v>
       </c>
       <c r="E20" t="n">
-        <v>292.162248007779</v>
+        <v>292.082248007779</v>
       </c>
       <c r="F20" t="n">
-        <v>207.4252493128175</v>
+        <v>207.3452493128175</v>
       </c>
       <c r="G20" t="n">
-        <v>125.2531916248005</v>
+        <v>125.1731916248005</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K20" t="n">
-        <v>312.6439213047977</v>
+        <v>312.5639213047978</v>
       </c>
       <c r="L20" t="n">
-        <v>532.4642177872098</v>
+        <v>954.0839213047977</v>
       </c>
       <c r="M20" t="n">
-        <v>999.286970190582</v>
+        <v>1595.603921304801</v>
       </c>
       <c r="N20" t="n">
-        <v>1641.796970190582</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="O20" t="n">
-        <v>1806.950481322281</v>
+        <v>1802.950481322281</v>
       </c>
       <c r="P20" t="n">
-        <v>2006.976374796579</v>
+        <v>2002.976374796579</v>
       </c>
       <c r="Q20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R20" t="n">
-        <v>2594.597071794846</v>
+        <v>2592</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U20" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V20" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X20" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1141.041188948283</v>
+        <v>168.2339162210096</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.536226882101</v>
+        <v>127.7289541548285</v>
       </c>
       <c r="D21" t="n">
-        <v>749.084017894523</v>
+        <v>100.5191694096743</v>
       </c>
       <c r="E21" t="n">
-        <v>402.9505863572374</v>
+        <v>78.62816211481311</v>
       </c>
       <c r="F21" t="n">
-        <v>59.88367490483648</v>
+        <v>59.80367490483648</v>
       </c>
       <c r="G21" t="n">
-        <v>55.85669946408083</v>
+        <v>55.77669946408083</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J21" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K21" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L21" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M21" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N21" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P21" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2080.925925057003</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S21" t="n">
-        <v>1948.016319603899</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T21" t="n">
-        <v>1865.871540558192</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U21" t="n">
-        <v>1785.911104741727</v>
+        <v>1591.157652543431</v>
       </c>
       <c r="V21" t="n">
-        <v>1496.782433158057</v>
+        <v>1172.460008915633</v>
       </c>
       <c r="W21" t="n">
-        <v>1384.284309006715</v>
+        <v>735.7194605218667</v>
       </c>
       <c r="X21" t="n">
-        <v>1284.422956031576</v>
+        <v>311.6156833043036</v>
       </c>
       <c r="Y21" t="n">
-        <v>1205.239731015279</v>
+        <v>232.4324582880062</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6904483778065</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4824541962423</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5915983212424</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E22" t="n">
-        <v>809.2105025326554</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F22" t="n">
-        <v>855.3614751245908</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1828770770499</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H22" t="n">
-        <v>1028.044822892185</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.758226418432</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J22" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K22" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L22" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M22" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N22" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O22" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P22" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R22" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S22" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8307078626652</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4421007486112</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W22" t="n">
-        <v>547.1230190082886</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X22" t="n">
-        <v>619.9438100324821</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.1431107115144</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.7843919601175</v>
+        <v>593.784391960133</v>
       </c>
       <c r="C23" t="n">
-        <v>468.0120907045681</v>
+        <v>464.0120907045836</v>
       </c>
       <c r="D23" t="n">
-        <v>377.7705192501743</v>
+        <v>373.7705192501898</v>
       </c>
       <c r="E23" t="n">
-        <v>293.5651762129333</v>
+        <v>289.5651762129488</v>
       </c>
       <c r="F23" t="n">
-        <v>208.8281775179718</v>
+        <v>204.8281775179873</v>
       </c>
       <c r="G23" t="n">
-        <v>126.6561198299548</v>
+        <v>122.6561198299703</v>
       </c>
       <c r="H23" t="n">
-        <v>53.32292820515431</v>
+        <v>51.84</v>
       </c>
       <c r="I23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J23" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K23" t="n">
-        <v>312.6439213047977</v>
+        <v>776.4566737081675</v>
       </c>
       <c r="L23" t="n">
-        <v>532.4642177872098</v>
+        <v>996.2769701905796</v>
       </c>
       <c r="M23" t="n">
-        <v>999.286970190582</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="N23" t="n">
-        <v>1641.796970190582</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="O23" t="n">
-        <v>1806.950481322281</v>
+        <v>1802.950481322281</v>
       </c>
       <c r="P23" t="n">
-        <v>2006.976374796579</v>
+        <v>2002.976374796579</v>
       </c>
       <c r="Q23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2592.000000000015</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.782470977807</v>
+        <v>2448.782470977822</v>
       </c>
       <c r="T23" t="n">
-        <v>2190.644809113007</v>
+        <v>2186.644809113022</v>
       </c>
       <c r="U23" t="n">
-        <v>1859.221845744784</v>
+        <v>1855.2218457448</v>
       </c>
       <c r="V23" t="n">
-        <v>1547.251114263144</v>
+        <v>1543.251114263159</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.67184559552</v>
+        <v>1222.671845595536</v>
       </c>
       <c r="X23" t="n">
-        <v>952.6497915948457</v>
+        <v>948.6497915948612</v>
       </c>
       <c r="Y23" t="n">
-        <v>760.4099606021121</v>
+        <v>756.4099606021275</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1257.955901870889</v>
+        <v>816.7187647058582</v>
       </c>
       <c r="C24" t="n">
-        <v>1217.450939804708</v>
+        <v>776.2138026396772</v>
       </c>
       <c r="D24" t="n">
-        <v>865.9987308171299</v>
+        <v>424.7615936520987</v>
       </c>
       <c r="E24" t="n">
-        <v>519.8652992798443</v>
+        <v>402.8705863572374</v>
       </c>
       <c r="F24" t="n">
-        <v>176.7983878274434</v>
+        <v>59.80367490483648</v>
       </c>
       <c r="G24" t="n">
-        <v>55.85669946408083</v>
+        <v>55.77669946408083</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J24" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K24" t="n">
-        <v>555.8339306093051</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L24" t="n">
-        <v>989.0096988082788</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M24" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N24" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O24" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P24" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2184.512931092847</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2003.167185781314</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S24" t="n">
-        <v>1870.25758032821</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T24" t="n">
-        <v>1788.112801282503</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U24" t="n">
-        <v>1708.152365466038</v>
+        <v>1785.831104741727</v>
       </c>
       <c r="V24" t="n">
-        <v>1613.697146080664</v>
+        <v>1691.375885356353</v>
       </c>
       <c r="W24" t="n">
-        <v>1501.199021929322</v>
+        <v>1384.204309006715</v>
       </c>
       <c r="X24" t="n">
-        <v>1401.337668954183</v>
+        <v>1284.342956031576</v>
       </c>
       <c r="Y24" t="n">
-        <v>1322.154443937886</v>
+        <v>880.9173067728548</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C25" t="n">
-        <v>723.3789473147295</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D25" t="n">
-        <v>758.4880914397296</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E25" t="n">
-        <v>798.1069956511426</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F25" t="n">
-        <v>844.257968243078</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G25" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H25" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I25" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J25" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K25" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L25" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M25" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N25" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O25" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P25" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R25" t="n">
-        <v>82.60111047978445</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S25" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T25" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U25" t="n">
-        <v>332.8307078626652</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V25" t="n">
-        <v>453.4421007486112</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W25" t="n">
-        <v>547.1230190082886</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X25" t="n">
-        <v>619.9438100324821</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.1431107115144</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C26" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045681</v>
       </c>
       <c r="D26" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501743</v>
       </c>
       <c r="E26" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129333</v>
       </c>
       <c r="F26" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179718</v>
       </c>
       <c r="G26" t="n">
-        <v>125.2531916248005</v>
+        <v>125.1731916248005</v>
       </c>
       <c r="H26" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="I26" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="J26" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K26" t="n">
-        <v>312.6439213047977</v>
+        <v>776.8935720585665</v>
       </c>
       <c r="L26" t="n">
-        <v>532.4642177872098</v>
+        <v>996.7138685409786</v>
       </c>
       <c r="M26" t="n">
-        <v>668.4699999999996</v>
+        <v>1585.300595394003</v>
       </c>
       <c r="N26" t="n">
-        <v>1310.979999999999</v>
+        <v>2226.820595394003</v>
       </c>
       <c r="O26" t="n">
-        <v>1953.489999999999</v>
+        <v>2391.974106525702</v>
       </c>
       <c r="P26" t="n">
-        <v>2595.999999999998</v>
+        <v>2592</v>
       </c>
       <c r="Q26" t="n">
-        <v>2595.999999999998</v>
+        <v>2592</v>
       </c>
       <c r="R26" t="n">
-        <v>2594.597071794846</v>
+        <v>2592</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U26" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V26" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X26" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1257.955901870889</v>
+        <v>362.9073684193053</v>
       </c>
       <c r="C27" t="n">
-        <v>1217.450939804708</v>
+        <v>322.4024063531242</v>
       </c>
       <c r="D27" t="n">
-        <v>1190.241155059554</v>
+        <v>295.19262160797</v>
       </c>
       <c r="E27" t="n">
-        <v>844.1077235222681</v>
+        <v>273.3016143131088</v>
       </c>
       <c r="F27" t="n">
-        <v>501.0408120698672</v>
+        <v>254.4771271031321</v>
       </c>
       <c r="G27" t="n">
-        <v>172.7714123866872</v>
+        <v>250.4501516623765</v>
       </c>
       <c r="H27" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="I27" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="J27" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K27" t="n">
-        <v>555.833930609305</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L27" t="n">
-        <v>989.0096988082787</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M27" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N27" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P27" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2184.512931092846</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2003.167185781314</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S27" t="n">
-        <v>1870.257580328209</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T27" t="n">
-        <v>1788.112801282502</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U27" t="n">
-        <v>1708.152365466038</v>
+        <v>1785.831104741727</v>
       </c>
       <c r="V27" t="n">
-        <v>1613.697146080664</v>
+        <v>1691.375885356353</v>
       </c>
       <c r="W27" t="n">
-        <v>1501.199021929322</v>
+        <v>1254.635336962587</v>
       </c>
       <c r="X27" t="n">
-        <v>1401.337668954183</v>
+        <v>830.5315597450235</v>
       </c>
       <c r="Y27" t="n">
-        <v>1322.154443937886</v>
+        <v>427.1059104863019</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C28" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4024541962424</v>
       </c>
       <c r="D28" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5115983212424</v>
       </c>
       <c r="E28" t="n">
-        <v>798.1069956511426</v>
+        <v>809.1305025326554</v>
       </c>
       <c r="F28" t="n">
-        <v>844.257968243078</v>
+        <v>855.2814751245909</v>
       </c>
       <c r="G28" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H28" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I28" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J28" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K28" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L28" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M28" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N28" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O28" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P28" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R28" t="n">
-        <v>82.6011104797844</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S28" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="T28" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U28" t="n">
-        <v>332.8307078626652</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V28" t="n">
-        <v>442.3385938670984</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W28" t="n">
-        <v>536.0195121267758</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X28" t="n">
-        <v>608.8403031509694</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y28" t="n">
-        <v>642.0396038300016</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.3814637549632</v>
+        <v>596.3014637549633</v>
       </c>
       <c r="C29" t="n">
-        <v>466.6091624994138</v>
+        <v>466.5291624994138</v>
       </c>
       <c r="D29" t="n">
-        <v>376.36759104502</v>
+        <v>376.2875910450201</v>
       </c>
       <c r="E29" t="n">
-        <v>292.162248007779</v>
+        <v>292.082248007779</v>
       </c>
       <c r="F29" t="n">
-        <v>207.4252493128175</v>
+        <v>207.3452493128175</v>
       </c>
       <c r="G29" t="n">
-        <v>125.2531916248005</v>
+        <v>125.1731916248006</v>
       </c>
       <c r="H29" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="I29" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="J29" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K29" t="n">
-        <v>312.6439213047977</v>
+        <v>776.8935720585665</v>
       </c>
       <c r="L29" t="n">
-        <v>532.4642177872098</v>
+        <v>1418.413572058566</v>
       </c>
       <c r="M29" t="n">
-        <v>1174.974217787209</v>
+        <v>1585.300595394003</v>
       </c>
       <c r="N29" t="n">
-        <v>1641.79697019058</v>
+        <v>2226.820595394003</v>
       </c>
       <c r="O29" t="n">
-        <v>1806.950481322279</v>
+        <v>2391.974106525702</v>
       </c>
       <c r="P29" t="n">
-        <v>2006.976374796577</v>
+        <v>2592</v>
       </c>
       <c r="Q29" t="n">
-        <v>2595.999999999998</v>
+        <v>2592</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.999999999998</v>
+        <v>2592</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.379542772653</v>
+        <v>2451.299542772653</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.241880907853</v>
+        <v>2189.161880907853</v>
       </c>
       <c r="U29" t="n">
-        <v>1857.81891753963</v>
+        <v>1857.73891753963</v>
       </c>
       <c r="V29" t="n">
-        <v>1545.84818605799</v>
+        <v>1545.76818605799</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.268917390366</v>
+        <v>1225.188917390366</v>
       </c>
       <c r="X29" t="n">
-        <v>951.2468633896915</v>
+        <v>951.1668633896916</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.0070323969577</v>
+        <v>758.9270323969578</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1141.041188948282</v>
+        <v>609.3910533860408</v>
       </c>
       <c r="C30" t="n">
-        <v>776.293802639677</v>
+        <v>568.8860913198597</v>
       </c>
       <c r="D30" t="n">
-        <v>749.0840178945228</v>
+        <v>541.6763065747056</v>
       </c>
       <c r="E30" t="n">
-        <v>402.9505863572373</v>
+        <v>519.7852992798444</v>
       </c>
       <c r="F30" t="n">
-        <v>59.88367490483643</v>
+        <v>176.7183878274435</v>
       </c>
       <c r="G30" t="n">
-        <v>55.85669946408078</v>
+        <v>172.6914123866878</v>
       </c>
       <c r="H30" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="I30" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="J30" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K30" t="n">
-        <v>555.833930609305</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L30" t="n">
-        <v>989.0096988082787</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M30" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N30" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O30" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P30" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2262.271670368536</v>
+        <v>2184.432931092847</v>
       </c>
       <c r="R30" t="n">
-        <v>2080.925925057003</v>
+        <v>2003.087185781314</v>
       </c>
       <c r="S30" t="n">
-        <v>1948.016319603898</v>
+        <v>1545.935156085785</v>
       </c>
       <c r="T30" t="n">
-        <v>1865.871540558192</v>
+        <v>1463.790377040079</v>
       </c>
       <c r="U30" t="n">
-        <v>1785.911104741727</v>
+        <v>1383.829941223614</v>
       </c>
       <c r="V30" t="n">
-        <v>1691.455885356353</v>
+        <v>1289.37472183824</v>
       </c>
       <c r="W30" t="n">
-        <v>1578.957761205011</v>
+        <v>1176.876597686898</v>
       </c>
       <c r="X30" t="n">
-        <v>1479.096408229872</v>
+        <v>752.7728204693346</v>
       </c>
       <c r="Y30" t="n">
-        <v>1399.913183213575</v>
+        <v>673.5895954530373</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6104483778066</v>
       </c>
       <c r="C31" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4024541962424</v>
       </c>
       <c r="D31" t="n">
-        <v>758.4880914397296</v>
+        <v>769.5115983212424</v>
       </c>
       <c r="E31" t="n">
-        <v>798.1069956511426</v>
+        <v>809.1305025326554</v>
       </c>
       <c r="F31" t="n">
-        <v>844.257968243078</v>
+        <v>855.2814751245909</v>
       </c>
       <c r="G31" t="n">
-        <v>920.0793701955371</v>
+        <v>931.1028770770499</v>
       </c>
       <c r="H31" t="n">
-        <v>1016.941316010672</v>
+        <v>1027.964822892185</v>
       </c>
       <c r="I31" t="n">
-        <v>1178.654719536919</v>
+        <v>1189.678226418432</v>
       </c>
       <c r="J31" t="n">
-        <v>1505.704370025436</v>
+        <v>1516.727876906949</v>
       </c>
       <c r="K31" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L31" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057278</v>
       </c>
       <c r="M31" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N31" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P31" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R31" t="n">
-        <v>82.6011104797844</v>
+        <v>82.52111047978443</v>
       </c>
       <c r="S31" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="T31" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U31" t="n">
-        <v>332.8307078626652</v>
+        <v>332.7507078626653</v>
       </c>
       <c r="V31" t="n">
-        <v>453.4421007486112</v>
+        <v>453.3621007486113</v>
       </c>
       <c r="W31" t="n">
-        <v>547.1230190082886</v>
+        <v>547.0430190082886</v>
       </c>
       <c r="X31" t="n">
-        <v>608.8403031509694</v>
+        <v>619.8638100324822</v>
       </c>
       <c r="Y31" t="n">
-        <v>642.0396038300016</v>
+        <v>653.0631107115145</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.3814637549632</v>
+        <v>593.7843919601175</v>
       </c>
       <c r="C32" t="n">
-        <v>466.6091624994138</v>
+        <v>464.0120907045681</v>
       </c>
       <c r="D32" t="n">
-        <v>376.36759104502</v>
+        <v>373.7705192501743</v>
       </c>
       <c r="E32" t="n">
-        <v>292.162248007779</v>
+        <v>289.5651762129333</v>
       </c>
       <c r="F32" t="n">
-        <v>207.4252493128175</v>
+        <v>204.8281775179718</v>
       </c>
       <c r="G32" t="n">
-        <v>125.2531916248005</v>
+        <v>122.6561198299548</v>
       </c>
       <c r="H32" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="I32" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="J32" t="n">
-        <v>135.4535720585666</v>
+        <v>135.3735720585666</v>
       </c>
       <c r="K32" t="n">
-        <v>312.6439213047977</v>
+        <v>312.5639213047978</v>
       </c>
       <c r="L32" t="n">
-        <v>532.4642177872098</v>
+        <v>532.3842177872099</v>
       </c>
       <c r="M32" t="n">
-        <v>999.2869701905806</v>
+        <v>1173.90421778721</v>
       </c>
       <c r="N32" t="n">
-        <v>1641.79697019058</v>
+        <v>1637.796970190582</v>
       </c>
       <c r="O32" t="n">
-        <v>1806.950481322279</v>
+        <v>1802.950481322281</v>
       </c>
       <c r="P32" t="n">
-        <v>2006.976374796577</v>
+        <v>2002.976374796579</v>
       </c>
       <c r="Q32" t="n">
-        <v>2595.999999999998</v>
+        <v>2592</v>
       </c>
       <c r="R32" t="n">
-        <v>2594.597071794846</v>
+        <v>2592</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.379542772653</v>
+        <v>2448.782470977807</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.241880907853</v>
+        <v>2186.644809113007</v>
       </c>
       <c r="U32" t="n">
-        <v>1857.81891753963</v>
+        <v>1855.221845744784</v>
       </c>
       <c r="V32" t="n">
-        <v>1545.84818605799</v>
+        <v>1543.251114263144</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.268917390366</v>
+        <v>1222.67184559552</v>
       </c>
       <c r="X32" t="n">
-        <v>951.2468633896915</v>
+        <v>948.6497915948457</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.0070323969577</v>
+        <v>756.4099606021121</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.3139162210096</v>
+        <v>492.4763404634339</v>
       </c>
       <c r="C33" t="n">
-        <v>127.8089541548285</v>
+        <v>451.9713783972528</v>
       </c>
       <c r="D33" t="n">
-        <v>100.5991694096743</v>
+        <v>100.5191694096743</v>
       </c>
       <c r="E33" t="n">
-        <v>78.70816211481306</v>
+        <v>78.62816211481311</v>
       </c>
       <c r="F33" t="n">
-        <v>59.88367490483643</v>
+        <v>59.80367490483648</v>
       </c>
       <c r="G33" t="n">
-        <v>55.85669946408078</v>
+        <v>55.77669946408083</v>
       </c>
       <c r="H33" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="I33" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="J33" t="n">
-        <v>246.2912041375631</v>
+        <v>246.2112041375631</v>
       </c>
       <c r="K33" t="n">
-        <v>555.833930609305</v>
+        <v>555.753930609305</v>
       </c>
       <c r="L33" t="n">
-        <v>989.0096988082787</v>
+        <v>988.9296988082788</v>
       </c>
       <c r="M33" t="n">
-        <v>1263.932740551138</v>
+        <v>1263.852740551138</v>
       </c>
       <c r="N33" t="n">
-        <v>1591.05362421531</v>
+        <v>1590.97362421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2007.422354200916</v>
+        <v>2007.342354200916</v>
       </c>
       <c r="P33" t="n">
-        <v>2262.271670368536</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2184.512931092846</v>
+        <v>2262.191670368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2003.167185781314</v>
+        <v>2080.845925057003</v>
       </c>
       <c r="S33" t="n">
-        <v>1870.257580328209</v>
+        <v>1947.936319603898</v>
       </c>
       <c r="T33" t="n">
-        <v>1788.112801282502</v>
+        <v>1865.791540558192</v>
       </c>
       <c r="U33" t="n">
-        <v>1383.909941223613</v>
+        <v>1591.157652543431</v>
       </c>
       <c r="V33" t="n">
-        <v>965.2122975958152</v>
+        <v>1172.460008915633</v>
       </c>
       <c r="W33" t="n">
-        <v>528.4717492020491</v>
+        <v>735.7194605218668</v>
       </c>
       <c r="X33" t="n">
-        <v>311.6956833043035</v>
+        <v>635.8581075467279</v>
       </c>
       <c r="Y33" t="n">
-        <v>232.5124582880062</v>
+        <v>556.6748825304305</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>675.5869414962938</v>
+        <v>675.5069414962938</v>
       </c>
       <c r="C34" t="n">
-        <v>723.3789473147295</v>
+        <v>723.2989473147296</v>
       </c>
       <c r="D34" t="n">
-        <v>758.4880914397296</v>
+        <v>758.4080914397297</v>
       </c>
       <c r="E34" t="n">
-        <v>798.1069956511426</v>
+        <v>798.0269956511427</v>
       </c>
       <c r="F34" t="n">
-        <v>844.257968243078</v>
+        <v>844.1779682430781</v>
       </c>
       <c r="G34" t="n">
-        <v>920.0793701955371</v>
+        <v>919.9993701955372</v>
       </c>
       <c r="H34" t="n">
-        <v>1016.941316010672</v>
+        <v>1016.861316010672</v>
       </c>
       <c r="I34" t="n">
-        <v>1178.654719536919</v>
+        <v>1178.574719536919</v>
       </c>
       <c r="J34" t="n">
-        <v>1505.704370025436</v>
+        <v>1505.624370025436</v>
       </c>
       <c r="K34" t="n">
-        <v>1610.453394126239</v>
+        <v>1610.373394126239</v>
       </c>
       <c r="L34" t="n">
-        <v>1601.652180057278</v>
+        <v>1601.572180057279</v>
       </c>
       <c r="M34" t="n">
-        <v>1499.938679551308</v>
+        <v>1499.858679551308</v>
       </c>
       <c r="N34" t="n">
-        <v>1344.784852898339</v>
+        <v>1344.704852898339</v>
       </c>
       <c r="O34" t="n">
-        <v>1112.223511470621</v>
+        <v>1112.143511470621</v>
       </c>
       <c r="P34" t="n">
-        <v>819.1796012698439</v>
+        <v>819.0996012698439</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.6348877086338</v>
+        <v>463.5548877086338</v>
       </c>
       <c r="R34" t="n">
-        <v>82.6011104797844</v>
+        <v>82.52111047978445</v>
       </c>
       <c r="S34" t="n">
-        <v>51.91999999999997</v>
+        <v>51.84</v>
       </c>
       <c r="T34" t="n">
-        <v>164.4554332571655</v>
+        <v>164.3754332571655</v>
       </c>
       <c r="U34" t="n">
-        <v>332.8307078626652</v>
+        <v>321.6472009811525</v>
       </c>
       <c r="V34" t="n">
-        <v>453.4421007486112</v>
+        <v>442.2585938670985</v>
       </c>
       <c r="W34" t="n">
-        <v>547.1230190082886</v>
+        <v>535.9395121267759</v>
       </c>
       <c r="X34" t="n">
-        <v>608.8403031509694</v>
+        <v>608.7603031509694</v>
       </c>
       <c r="Y34" t="n">
-        <v>642.0396038300016</v>
+        <v>641.9596038300017</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>443.726918300419</v>
+        <v>444.1269183004177</v>
       </c>
       <c r="C35" t="n">
-        <v>338.1970412872938</v>
+        <v>338.5970412872925</v>
       </c>
       <c r="D35" t="n">
-        <v>272.1978940753243</v>
+        <v>272.597894075323</v>
       </c>
       <c r="E35" t="n">
-        <v>212.2349752805075</v>
+        <v>212.6349752805062</v>
       </c>
       <c r="F35" t="n">
-        <v>151.7404008279703</v>
+        <v>152.140400827969</v>
       </c>
       <c r="G35" t="n">
-        <v>93.81076738237753</v>
+        <v>94.21076738237628</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J35" t="n">
-        <v>128.2535720585678</v>
+        <v>554.6552612788618</v>
       </c>
       <c r="K35" t="n">
-        <v>305.443921304799</v>
+        <v>731.845610525093</v>
       </c>
       <c r="L35" t="n">
-        <v>525.2642177872111</v>
+        <v>1290.205610525093</v>
       </c>
       <c r="M35" t="n">
-        <v>1078.674217787217</v>
+        <v>1848.565610525093</v>
       </c>
       <c r="N35" t="n">
-        <v>1317.410595394059</v>
+        <v>1890.820595394003</v>
       </c>
       <c r="O35" t="n">
-        <v>1482.564106525758</v>
+        <v>2055.974106525702</v>
       </c>
       <c r="P35" t="n">
-        <v>1682.590000000056</v>
+        <v>2256</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="R35" t="n">
-        <v>2236.000000000061</v>
+        <v>2248.403132400907</v>
       </c>
       <c r="S35" t="n">
-        <v>2117.024895220292</v>
+        <v>2129.428027621138</v>
       </c>
       <c r="T35" t="n">
-        <v>1879.129657597917</v>
+        <v>1891.532789998762</v>
       </c>
       <c r="U35" t="n">
-        <v>1571.949118472118</v>
+        <v>1584.352250872963</v>
       </c>
       <c r="V35" t="n">
-        <v>1284.220811232902</v>
+        <v>1296.623943633747</v>
       </c>
       <c r="W35" t="n">
-        <v>987.8839668077028</v>
+        <v>1000.287099208548</v>
       </c>
       <c r="X35" t="n">
-        <v>738.1043370494526</v>
+        <v>750.5074694502975</v>
       </c>
       <c r="Y35" t="n">
-        <v>582.1100626999893</v>
+        <v>582.510062699988</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1449.866049684234</v>
+        <v>758.9681783486208</v>
       </c>
       <c r="C36" t="n">
-        <v>1413.641951660446</v>
+        <v>394.2207920400155</v>
       </c>
       <c r="D36" t="n">
-        <v>1062.189742672868</v>
+        <v>391.2534315372855</v>
       </c>
       <c r="E36" t="n">
-        <v>716.0563111355821</v>
+        <v>45.12</v>
       </c>
       <c r="F36" t="n">
-        <v>372.9893996831811</v>
+        <v>45.12</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J36" t="n">
-        <v>239.0912041375643</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K36" t="n">
-        <v>548.6339306093063</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L36" t="n">
-        <v>962.7380284398043</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M36" t="n">
-        <v>1237.661070182663</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N36" t="n">
-        <v>1564.781953846836</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1981.150683832441</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P36" t="n">
-        <v>2236.000000000061</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>2158.241260724372</v>
+        <v>2177.712931092847</v>
       </c>
       <c r="R36" t="n">
-        <v>2001.137939655264</v>
+        <v>2020.609610023739</v>
       </c>
       <c r="S36" t="n">
-        <v>1892.470758444584</v>
+        <v>1911.942428813058</v>
       </c>
       <c r="T36" t="n">
-        <v>1834.568403641301</v>
+        <v>1854.040074009776</v>
       </c>
       <c r="U36" t="n">
-        <v>1778.850392067261</v>
+        <v>1784.922217701346</v>
       </c>
       <c r="V36" t="n">
-        <v>1708.637596924311</v>
+        <v>1714.709422558396</v>
       </c>
       <c r="W36" t="n">
-        <v>1620.381897015394</v>
+        <v>1626.453722649478</v>
       </c>
       <c r="X36" t="n">
-        <v>1544.762968282679</v>
+        <v>1550.834793916763</v>
       </c>
       <c r="Y36" t="n">
-        <v>1489.822167508806</v>
+        <v>1147.409144658042</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>463.4269259561675</v>
+        <v>652.6076774543488</v>
       </c>
       <c r="C37" t="n">
-        <v>534.9789317746032</v>
+        <v>724.1596832727846</v>
       </c>
       <c r="D37" t="n">
-        <v>534.9789317746032</v>
+        <v>783.0288273977847</v>
       </c>
       <c r="E37" t="n">
-        <v>598.3578359860162</v>
+        <v>846.4077316091976</v>
       </c>
       <c r="F37" t="n">
-        <v>668.2688085779517</v>
+        <v>916.3187042011332</v>
       </c>
       <c r="G37" t="n">
-        <v>767.8502105304108</v>
+        <v>916.3187042011332</v>
       </c>
       <c r="H37" t="n">
-        <v>888.4721563455461</v>
+        <v>916.3187042011332</v>
       </c>
       <c r="I37" t="n">
-        <v>1073.945559871793</v>
+        <v>1101.79210772738</v>
       </c>
       <c r="J37" t="n">
-        <v>1424.75521036031</v>
+        <v>1425.155210360309</v>
       </c>
       <c r="K37" t="n">
-        <v>1424.75521036031</v>
+        <v>1425.155210360309</v>
       </c>
       <c r="L37" t="n">
-        <v>1424.75521036031</v>
+        <v>1425.155210360309</v>
       </c>
       <c r="M37" t="n">
-        <v>1347.284134096764</v>
+        <v>1347.684134096763</v>
       </c>
       <c r="N37" t="n">
-        <v>1216.372731686219</v>
+        <v>1216.772731686218</v>
       </c>
       <c r="O37" t="n">
-        <v>1008.053814500925</v>
+        <v>1008.453814500924</v>
       </c>
       <c r="P37" t="n">
-        <v>739.2523285425725</v>
+        <v>739.6523285425712</v>
       </c>
       <c r="Q37" t="n">
-        <v>407.9500392237866</v>
+        <v>408.3500392237853</v>
       </c>
       <c r="R37" t="n">
-        <v>51.15868623736142</v>
+        <v>51.55868623736021</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="T37" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="U37" t="n">
-        <v>44.72000000000123</v>
+        <v>237.2552746054997</v>
       </c>
       <c r="V37" t="n">
-        <v>135.1385783269722</v>
+        <v>381.6266674914457</v>
       </c>
       <c r="W37" t="n">
-        <v>252.5794965866496</v>
+        <v>499.0675857511231</v>
       </c>
       <c r="X37" t="n">
-        <v>349.1602876108431</v>
+        <v>595.6483767753166</v>
       </c>
       <c r="Y37" t="n">
-        <v>406.1195882898753</v>
+        <v>652.6076774543488</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>443.726918300419</v>
+        <v>451.7237858995115</v>
       </c>
       <c r="C38" t="n">
-        <v>338.1970412872938</v>
+        <v>346.1939088863863</v>
       </c>
       <c r="D38" t="n">
-        <v>272.1978940753243</v>
+        <v>280.1947616744168</v>
       </c>
       <c r="E38" t="n">
-        <v>212.2349752805075</v>
+        <v>220.2318428796</v>
       </c>
       <c r="F38" t="n">
-        <v>151.7404008279703</v>
+        <v>159.7372684270628</v>
       </c>
       <c r="G38" t="n">
-        <v>93.81076738237753</v>
+        <v>101.80763498147</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72000000000123</v>
+        <v>52.71686759909374</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J38" t="n">
-        <v>554.255261278863</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K38" t="n">
-        <v>1097.590298911649</v>
+        <v>305.8439213047978</v>
       </c>
       <c r="L38" t="n">
-        <v>1317.410595394061</v>
+        <v>864.2039213047977</v>
       </c>
       <c r="M38" t="n">
-        <v>1870.820595394064</v>
+        <v>864.2039213047977</v>
       </c>
       <c r="N38" t="n">
-        <v>1870.820595394064</v>
+        <v>1332.460595394003</v>
       </c>
       <c r="O38" t="n">
-        <v>2035.974106525763</v>
+        <v>1497.614106525702</v>
       </c>
       <c r="P38" t="n">
-        <v>2236.000000000061</v>
+        <v>1697.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="R38" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="S38" t="n">
-        <v>2129.028027621139</v>
+        <v>2137.024895220231</v>
       </c>
       <c r="T38" t="n">
-        <v>1891.132789998763</v>
+        <v>1899.129657597855</v>
       </c>
       <c r="U38" t="n">
-        <v>1583.952250872965</v>
+        <v>1591.949118472057</v>
       </c>
       <c r="V38" t="n">
-        <v>1296.223943633749</v>
+        <v>1304.220811232841</v>
       </c>
       <c r="W38" t="n">
-        <v>999.887099208549</v>
+        <v>1007.883966807641</v>
       </c>
       <c r="X38" t="n">
-        <v>750.1074694502988</v>
+        <v>758.1043370493912</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.1100626999893</v>
+        <v>590.1069302990818</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1450.119938285872</v>
+        <v>1450.51993828587</v>
       </c>
       <c r="C39" t="n">
-        <v>1085.372551977266</v>
+        <v>1085.772551977265</v>
       </c>
       <c r="D39" t="n">
-        <v>733.9203429896877</v>
+        <v>734.3203429896864</v>
       </c>
       <c r="E39" t="n">
-        <v>387.7869114524021</v>
+        <v>388.1869114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J39" t="n">
-        <v>239.0912041375643</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K39" t="n">
-        <v>548.6339306093063</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L39" t="n">
-        <v>981.80969880828</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M39" t="n">
-        <v>1256.732740551139</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N39" t="n">
-        <v>1564.781953846836</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1981.150683832441</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P39" t="n">
-        <v>2236.000000000061</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>2158.495149326011</v>
+        <v>2177.712931092847</v>
       </c>
       <c r="R39" t="n">
-        <v>2001.391828256902</v>
+        <v>2020.609610023739</v>
       </c>
       <c r="S39" t="n">
-        <v>1892.724647046222</v>
+        <v>1893.124647046221</v>
       </c>
       <c r="T39" t="n">
-        <v>1834.82229224294</v>
+        <v>1835.222292242938</v>
       </c>
       <c r="U39" t="n">
-        <v>1779.104280668899</v>
+        <v>1779.504280668898</v>
       </c>
       <c r="V39" t="n">
-        <v>1708.891485525949</v>
+        <v>1709.291485525948</v>
       </c>
       <c r="W39" t="n">
-        <v>1620.635785617032</v>
+        <v>1621.03578561703</v>
       </c>
       <c r="X39" t="n">
-        <v>1545.016856884317</v>
+        <v>1545.416856884316</v>
       </c>
       <c r="Y39" t="n">
-        <v>1490.076056110444</v>
+        <v>1490.476056110443</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>260.9148276393528</v>
+        <v>602.8648276393517</v>
       </c>
       <c r="C40" t="n">
-        <v>332.4668334577885</v>
+        <v>674.4168334577874</v>
       </c>
       <c r="D40" t="n">
-        <v>391.3359775827886</v>
+        <v>733.2859775827875</v>
       </c>
       <c r="E40" t="n">
-        <v>454.7148817942016</v>
+        <v>796.6648817942005</v>
       </c>
       <c r="F40" t="n">
-        <v>524.6258543861371</v>
+        <v>866.5758543861359</v>
       </c>
       <c r="G40" t="n">
-        <v>624.2072563385962</v>
+        <v>966.1572563385949</v>
       </c>
       <c r="H40" t="n">
-        <v>744.8292021537314</v>
+        <v>1086.77920215373</v>
       </c>
       <c r="I40" t="n">
-        <v>930.3026056799783</v>
+        <v>1272.252605679977</v>
       </c>
       <c r="J40" t="n">
-        <v>1281.112256168495</v>
+        <v>1281.512256168494</v>
       </c>
       <c r="K40" t="n">
-        <v>1409.621280269298</v>
+        <v>1410.021280269297</v>
       </c>
       <c r="L40" t="n">
-        <v>1424.75521036031</v>
+        <v>1425.155210360309</v>
       </c>
       <c r="M40" t="n">
-        <v>1347.284134096764</v>
+        <v>1347.684134096763</v>
       </c>
       <c r="N40" t="n">
-        <v>1216.372731686219</v>
+        <v>1216.772731686218</v>
       </c>
       <c r="O40" t="n">
-        <v>1008.053814500925</v>
+        <v>1008.453814500924</v>
       </c>
       <c r="P40" t="n">
-        <v>739.2523285425725</v>
+        <v>739.6523285425712</v>
       </c>
       <c r="Q40" t="n">
-        <v>407.9500392237866</v>
+        <v>408.3500392237854</v>
       </c>
       <c r="R40" t="n">
-        <v>51.15868623736142</v>
+        <v>51.55868623736018</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="T40" t="n">
-        <v>146.6481892940284</v>
+        <v>181.4154332571655</v>
       </c>
       <c r="U40" t="n">
-        <v>146.6481892940284</v>
+        <v>187.1643878032427</v>
       </c>
       <c r="V40" t="n">
-        <v>146.6481892940284</v>
+        <v>331.5357806891886</v>
       </c>
       <c r="W40" t="n">
-        <v>146.6481892940284</v>
+        <v>448.976698948866</v>
       </c>
       <c r="X40" t="n">
-        <v>146.6481892940284</v>
+        <v>545.5574899730595</v>
       </c>
       <c r="Y40" t="n">
-        <v>203.6074899730606</v>
+        <v>545.5574899730595</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>569.2073553284017</v>
+        <v>257.7843919601178</v>
       </c>
       <c r="C41" t="n">
-        <v>439.4350540728523</v>
+        <v>128.0120907045684</v>
       </c>
       <c r="D41" t="n">
-        <v>349.1934826184585</v>
+        <v>118.4531916248006</v>
       </c>
       <c r="E41" t="n">
-        <v>264.9881395812175</v>
+        <v>118.4531916248006</v>
       </c>
       <c r="F41" t="n">
-        <v>180.251140886256</v>
+        <v>118.4531916248006</v>
       </c>
       <c r="G41" t="n">
-        <v>118.0531916248018</v>
+        <v>118.4531916248006</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J41" t="n">
-        <v>128.2535720585678</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K41" t="n">
-        <v>681.663572058583</v>
+        <v>305.8439213047978</v>
       </c>
       <c r="L41" t="n">
-        <v>901.4838685409951</v>
+        <v>774.1005953940031</v>
       </c>
       <c r="M41" t="n">
-        <v>1454.893868541</v>
+        <v>1332.460595394003</v>
       </c>
       <c r="N41" t="n">
-        <v>1517.436488868357</v>
+        <v>1890.820595394003</v>
       </c>
       <c r="O41" t="n">
-        <v>1682.590000000056</v>
+        <v>2055.974106525702</v>
       </c>
       <c r="P41" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="R41" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="S41" t="n">
-        <v>2092.782470977868</v>
+        <v>2112.782470977807</v>
       </c>
       <c r="T41" t="n">
-        <v>1830.644809113069</v>
+        <v>1850.644809113007</v>
       </c>
       <c r="U41" t="n">
-        <v>1830.644809113069</v>
+        <v>1519.221845744785</v>
       </c>
       <c r="V41" t="n">
-        <v>1518.674077631428</v>
+        <v>1207.251114263144</v>
       </c>
       <c r="W41" t="n">
-        <v>1198.094808963804</v>
+        <v>886.6718455955204</v>
       </c>
       <c r="X41" t="n">
-        <v>924.0727549631299</v>
+        <v>612.649791594846</v>
       </c>
       <c r="Y41" t="n">
-        <v>731.8329239703962</v>
+        <v>420.4099606021122</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>809.5987647058593</v>
+        <v>926.913477628465</v>
       </c>
       <c r="C42" t="n">
-        <v>769.0938026396782</v>
+        <v>562.1660913198596</v>
       </c>
       <c r="D42" t="n">
-        <v>741.884017894524</v>
+        <v>534.9563065747054</v>
       </c>
       <c r="E42" t="n">
-        <v>719.9930105996629</v>
+        <v>513.0652992798442</v>
       </c>
       <c r="F42" t="n">
-        <v>701.1685233896862</v>
+        <v>169.9983878274433</v>
       </c>
       <c r="G42" t="n">
-        <v>372.8991237065063</v>
+        <v>49.05669946408081</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J42" t="n">
-        <v>239.0912041375643</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K42" t="n">
-        <v>548.6339306093063</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L42" t="n">
-        <v>962.7380284397971</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M42" t="n">
-        <v>1237.661070182656</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N42" t="n">
-        <v>1564.781953846828</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1981.150683832434</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P42" t="n">
-        <v>2236.000000000054</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>2158.241260724365</v>
+        <v>2177.712931092847</v>
       </c>
       <c r="R42" t="n">
-        <v>1976.895515412833</v>
+        <v>1996.367185781314</v>
       </c>
       <c r="S42" t="n">
-        <v>1843.985909959728</v>
+        <v>1863.45758032821</v>
       </c>
       <c r="T42" t="n">
-        <v>1761.841130914021</v>
+        <v>1781.312801282503</v>
       </c>
       <c r="U42" t="n">
-        <v>1584.037652543432</v>
+        <v>1701.352365466038</v>
       </c>
       <c r="V42" t="n">
-        <v>1165.340008915634</v>
+        <v>1606.897146080664</v>
       </c>
       <c r="W42" t="n">
-        <v>1052.841884764292</v>
+        <v>1494.399021929322</v>
       </c>
       <c r="X42" t="n">
-        <v>952.9805317891531</v>
+        <v>1394.537668954183</v>
       </c>
       <c r="Y42" t="n">
-        <v>873.7973067728558</v>
+        <v>1315.354443937886</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>679.4904483778079</v>
+        <v>668.786941496294</v>
       </c>
       <c r="C43" t="n">
-        <v>727.2824541962436</v>
+        <v>716.5789473147298</v>
       </c>
       <c r="D43" t="n">
-        <v>762.3915983212437</v>
+        <v>751.6880914397299</v>
       </c>
       <c r="E43" t="n">
-        <v>802.0105025326567</v>
+        <v>791.3069956511429</v>
       </c>
       <c r="F43" t="n">
-        <v>848.1614751245921</v>
+        <v>837.4579682430783</v>
       </c>
       <c r="G43" t="n">
-        <v>923.9828770770512</v>
+        <v>913.2793701955374</v>
       </c>
       <c r="H43" t="n">
-        <v>1020.844822892186</v>
+        <v>1010.141316010673</v>
       </c>
       <c r="I43" t="n">
-        <v>1182.558226418433</v>
+        <v>1171.854719536919</v>
       </c>
       <c r="J43" t="n">
-        <v>1509.60787690695</v>
+        <v>1498.904370025436</v>
       </c>
       <c r="K43" t="n">
-        <v>1603.25339412624</v>
+        <v>1603.653394126239</v>
       </c>
       <c r="L43" t="n">
-        <v>1594.45218005728</v>
+        <v>1594.852180057278</v>
       </c>
       <c r="M43" t="n">
-        <v>1492.738679551309</v>
+        <v>1493.138679551308</v>
       </c>
       <c r="N43" t="n">
-        <v>1337.584852898341</v>
+        <v>1337.98485289834</v>
       </c>
       <c r="O43" t="n">
-        <v>1105.023511470622</v>
+        <v>1105.423511470621</v>
       </c>
       <c r="P43" t="n">
-        <v>811.9796012698451</v>
+        <v>812.379601269844</v>
       </c>
       <c r="Q43" t="n">
-        <v>456.4348877086351</v>
+        <v>456.8348877086339</v>
       </c>
       <c r="R43" t="n">
-        <v>75.40111047978566</v>
+        <v>75.80111047978443</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="T43" t="n">
-        <v>157.2554332571667</v>
+        <v>157.6554332571655</v>
       </c>
       <c r="U43" t="n">
-        <v>325.6307078626665</v>
+        <v>326.0307078626653</v>
       </c>
       <c r="V43" t="n">
-        <v>446.2421007486125</v>
+        <v>446.6421007486113</v>
       </c>
       <c r="W43" t="n">
-        <v>539.9230190082899</v>
+        <v>540.3230190082886</v>
       </c>
       <c r="X43" t="n">
-        <v>612.7438100324835</v>
+        <v>613.1438100324822</v>
       </c>
       <c r="Y43" t="n">
-        <v>645.9431107115157</v>
+        <v>646.3431107115144</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>589.1814637549644</v>
+        <v>589.5814637549632</v>
       </c>
       <c r="C44" t="n">
-        <v>459.409162499415</v>
+        <v>459.8091624994138</v>
       </c>
       <c r="D44" t="n">
-        <v>369.1675910450213</v>
+        <v>369.56759104502</v>
       </c>
       <c r="E44" t="n">
-        <v>284.9622480077802</v>
+        <v>285.362248007779</v>
       </c>
       <c r="F44" t="n">
-        <v>200.2252493128187</v>
+        <v>200.6252493128175</v>
       </c>
       <c r="G44" t="n">
-        <v>118.0531916248017</v>
+        <v>118.4531916248005</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J44" t="n">
-        <v>128.2535720585678</v>
+        <v>128.6535720585666</v>
       </c>
       <c r="K44" t="n">
-        <v>305.443921304799</v>
+        <v>687.0135720585666</v>
       </c>
       <c r="L44" t="n">
-        <v>525.2642177872111</v>
+        <v>906.8338685409786</v>
       </c>
       <c r="M44" t="n">
-        <v>1078.674217787218</v>
+        <v>974.1264888683012</v>
       </c>
       <c r="N44" t="n">
-        <v>1317.410595394057</v>
+        <v>1532.486488868301</v>
       </c>
       <c r="O44" t="n">
-        <v>1482.564106525756</v>
+        <v>1697.64</v>
       </c>
       <c r="P44" t="n">
-        <v>1682.590000000054</v>
+        <v>2256</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="R44" t="n">
-        <v>2236.000000000061</v>
+        <v>2256</v>
       </c>
       <c r="S44" t="n">
-        <v>2092.782470977868</v>
+        <v>2112.782470977807</v>
       </c>
       <c r="T44" t="n">
-        <v>1830.644809113069</v>
+        <v>2112.782470977807</v>
       </c>
       <c r="U44" t="n">
-        <v>1830.644809113069</v>
+        <v>1781.359507609584</v>
       </c>
       <c r="V44" t="n">
-        <v>1518.674077631428</v>
+        <v>1539.04818605799</v>
       </c>
       <c r="W44" t="n">
-        <v>1198.094808963804</v>
+        <v>1218.468917390366</v>
       </c>
       <c r="X44" t="n">
-        <v>924.0727549631299</v>
+        <v>944.4468633896915</v>
       </c>
       <c r="Y44" t="n">
-        <v>731.8329239703962</v>
+        <v>752.2070323969577</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>907.4418072599906</v>
+        <v>602.6710533860407</v>
       </c>
       <c r="C45" t="n">
-        <v>866.9368451938095</v>
+        <v>562.1660913198597</v>
       </c>
       <c r="D45" t="n">
-        <v>741.884017894524</v>
+        <v>534.9563065747055</v>
       </c>
       <c r="E45" t="n">
-        <v>395.7505863572386</v>
+        <v>396.1505863572374</v>
       </c>
       <c r="F45" t="n">
-        <v>52.68367490483772</v>
+        <v>377.3260991472608</v>
       </c>
       <c r="G45" t="n">
-        <v>48.65669946408205</v>
+        <v>373.2991237065051</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="J45" t="n">
-        <v>239.0912041375643</v>
+        <v>239.4912041375631</v>
       </c>
       <c r="K45" t="n">
-        <v>548.6339306093063</v>
+        <v>549.033930609305</v>
       </c>
       <c r="L45" t="n">
-        <v>962.7380284398043</v>
+        <v>982.2096988082787</v>
       </c>
       <c r="M45" t="n">
-        <v>1237.661070182663</v>
+        <v>1257.132740551138</v>
       </c>
       <c r="N45" t="n">
-        <v>1564.781953846836</v>
+        <v>1584.25362421531</v>
       </c>
       <c r="O45" t="n">
-        <v>1981.150683832441</v>
+        <v>2000.622354200916</v>
       </c>
       <c r="P45" t="n">
-        <v>2236.000000000061</v>
+        <v>2255.471670368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>2158.241260724372</v>
+        <v>2177.712931092847</v>
       </c>
       <c r="R45" t="n">
-        <v>1976.89551541284</v>
+        <v>1996.367185781314</v>
       </c>
       <c r="S45" t="n">
-        <v>1843.985909959735</v>
+        <v>1863.45758032821</v>
       </c>
       <c r="T45" t="n">
-        <v>1761.841130914028</v>
+        <v>1781.312801282503</v>
       </c>
       <c r="U45" t="n">
-        <v>1681.880695097564</v>
+        <v>1701.352365466038</v>
       </c>
       <c r="V45" t="n">
-        <v>1587.42547571219</v>
+        <v>1282.65472183824</v>
       </c>
       <c r="W45" t="n">
-        <v>1150.684927318423</v>
+        <v>845.9141734444736</v>
       </c>
       <c r="X45" t="n">
-        <v>1050.823574343284</v>
+        <v>746.0528204693346</v>
       </c>
       <c r="Y45" t="n">
-        <v>971.6403493269871</v>
+        <v>666.8695954530373</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>679.4904483778079</v>
+        <v>668.7869414962938</v>
       </c>
       <c r="C46" t="n">
-        <v>727.2824541962436</v>
+        <v>716.5789473147296</v>
       </c>
       <c r="D46" t="n">
-        <v>762.3915983212437</v>
+        <v>751.6880914397296</v>
       </c>
       <c r="E46" t="n">
-        <v>802.0105025326567</v>
+        <v>791.3069956511426</v>
       </c>
       <c r="F46" t="n">
-        <v>837.0579682430794</v>
+        <v>837.4579682430781</v>
       </c>
       <c r="G46" t="n">
-        <v>912.8793701955384</v>
+        <v>913.2793701955371</v>
       </c>
       <c r="H46" t="n">
-        <v>1009.741316010674</v>
+        <v>1010.141316010672</v>
       </c>
       <c r="I46" t="n">
-        <v>1171.45471953692</v>
+        <v>1171.854719536919</v>
       </c>
       <c r="J46" t="n">
-        <v>1498.504370025437</v>
+        <v>1498.904370025436</v>
       </c>
       <c r="K46" t="n">
-        <v>1603.25339412624</v>
+        <v>1603.653394126239</v>
       </c>
       <c r="L46" t="n">
-        <v>1594.45218005728</v>
+        <v>1594.852180057278</v>
       </c>
       <c r="M46" t="n">
-        <v>1492.738679551309</v>
+        <v>1493.138679551308</v>
       </c>
       <c r="N46" t="n">
-        <v>1337.584852898341</v>
+        <v>1337.984852898339</v>
       </c>
       <c r="O46" t="n">
-        <v>1105.023511470622</v>
+        <v>1105.423511470621</v>
       </c>
       <c r="P46" t="n">
-        <v>811.9796012698451</v>
+        <v>812.3796012698439</v>
       </c>
       <c r="Q46" t="n">
-        <v>456.4348877086351</v>
+        <v>456.8348877086338</v>
       </c>
       <c r="R46" t="n">
-        <v>75.40111047978567</v>
+        <v>75.80111047978446</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72000000000123</v>
+        <v>45.12</v>
       </c>
       <c r="T46" t="n">
-        <v>157.2554332571667</v>
+        <v>157.6554332571655</v>
       </c>
       <c r="U46" t="n">
-        <v>325.6307078626665</v>
+        <v>326.0307078626653</v>
       </c>
       <c r="V46" t="n">
-        <v>446.2421007486125</v>
+        <v>435.5385938670984</v>
       </c>
       <c r="W46" t="n">
-        <v>539.9230190082899</v>
+        <v>529.2195121267758</v>
       </c>
       <c r="X46" t="n">
-        <v>612.7438100324835</v>
+        <v>602.0403031509694</v>
       </c>
       <c r="Y46" t="n">
-        <v>645.9431107115157</v>
+        <v>635.2396038300017</v>
       </c>
     </row>
   </sheetData>
@@ -7964,19 +7964,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>181.5167089435054</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="M2" t="n">
-        <v>845.5549969890515</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>777.3653500296348</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
         <v>0.4816735941929551</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.1077446289935</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>373.899302727503</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.3286984924629</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M5" t="n">
-        <v>471.5549969890509</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>637.6540577531747</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
         <v>0.4816735941929551</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.1077446289935</v>
+        <v>427.6391621152114</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>845.5549969890515</v>
+        <v>705.843704712591</v>
       </c>
       <c r="N8" t="n">
-        <v>777.3653500296348</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>181.9983825376981</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.1077446289935</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8526,7 +8526,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M9" t="n">
-        <v>471.6948204301071</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N9" t="n">
         <v>485.4085271713503</v>
@@ -8678,16 +8678,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>470.0198492462312</v>
+        <v>469.0198492462312</v>
       </c>
       <c r="L11" t="n">
-        <v>426.9592964824121</v>
+        <v>425.9592964824119</v>
       </c>
       <c r="M11" t="n">
-        <v>466.7314091191549</v>
+        <v>945.1990623156852</v>
       </c>
       <c r="N11" t="n">
-        <v>875.1881540497347</v>
+        <v>394.760904893609</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>469.0198492462312</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>338.4324594703072</v>
+        <v>945.1990623156856</v>
       </c>
       <c r="N14" t="n">
-        <v>875.1881540497347</v>
+        <v>820.7202013760202</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9158,19 +9158,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>946.1990623156843</v>
+        <v>945.1990623156856</v>
       </c>
       <c r="N17" t="n">
-        <v>697.7262877905147</v>
+        <v>362.6081360828518</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>481.1782715841441</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>445.9536429552558</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9392,13 +9392,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>425.959296482412</v>
       </c>
       <c r="M20" t="n">
-        <v>768.7371960564642</v>
+        <v>945.1990623156875</v>
       </c>
       <c r="N20" t="n">
-        <v>875.1881540497347</v>
+        <v>268.8073953485033</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>468.5785377811816</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>768.7371960564642</v>
+        <v>945.1990623156865</v>
       </c>
       <c r="N23" t="n">
-        <v>875.1881540497347</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,22 +9863,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>469.0198492462312</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>434.5786403084011</v>
+        <v>891.7311096419711</v>
       </c>
       <c r="N26" t="n">
-        <v>875.1881540497343</v>
+        <v>874.1881540497347</v>
       </c>
       <c r="O26" t="n">
-        <v>482.1782715841422</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>446.9536429552538</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>20.87871447823917</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>469.0198492462312</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>425.9592964824119</v>
       </c>
       <c r="M29" t="n">
-        <v>946.1990623156837</v>
+        <v>465.7718131595593</v>
       </c>
       <c r="N29" t="n">
-        <v>697.7262877905132</v>
+        <v>874.1881540497347</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>768.7371960564628</v>
+        <v>945.1990623156843</v>
       </c>
       <c r="N32" t="n">
-        <v>875.1881540497343</v>
+        <v>694.7666918309188</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>341.959296482412</v>
       </c>
       <c r="M35" t="n">
-        <v>856.1990623156895</v>
+        <v>861.1990623156843</v>
       </c>
       <c r="N35" t="n">
-        <v>467.3360102182626</v>
+        <v>268.8699569476238</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>579.8787144782445</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10656,7 +10656,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>368.8250229562873</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>369.8431195823786</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>341.959296482412</v>
       </c>
       <c r="M38" t="n">
-        <v>856.1990623156877</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N38" t="n">
-        <v>226.1881540497347</v>
+        <v>699.1746935337803</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20.87871447823917</v>
+        <v>584.8787144782391</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10899,7 +10899,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>466.1442136678396</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11048,22 +11048,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>380.0198492462465</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>250.9458359664578</v>
       </c>
       <c r="M41" t="n">
-        <v>856.1990623156895</v>
+        <v>861.1990623156843</v>
       </c>
       <c r="N41" t="n">
-        <v>289.3625180167621</v>
+        <v>790.1881540497347</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>356.9536429552597</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>20.87871447823917</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>368.82502295628</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11285,25 +11285,25 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>385.0198492462312</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>856.1990623156913</v>
+        <v>365.1714060806563</v>
       </c>
       <c r="N44" t="n">
-        <v>467.3360102182589</v>
+        <v>790.1881540497347</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>361.9536429552543</v>
       </c>
       <c r="Q44" t="n">
-        <v>579.8787144782464</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,7 +11367,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>368.8250229562873</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22530,7 +22530,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.592258985321991e-12</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.491901076897236</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23520,7 +23520,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.491901076897136</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.491901076897364</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -23937,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.491901076897165</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.491901076881931</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.491901076897221</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.491901076897392</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2.491901076897236</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>11.88310107683768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>11.88310107683776</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25599,16 +25599,16 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>79.87584565087967</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>19.77436734229713</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25650,7 +25650,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>328.1087337345403</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.77436734229701</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25884,13 +25884,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U44" t="n">
-        <v>328.1087337345404</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>68.96281583074526</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3623129.37004924</v>
+        <v>3622895.96616972</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4504693.298282056</v>
+        <v>4504321.045674531</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5386257.226514872</v>
+        <v>5385746.125179342</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6267821.154747685</v>
+        <v>6267171.20468415</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7149385.082980499</v>
+        <v>7148596.28418896</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8030949.011213311</v>
+        <v>8030021.363693768</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8912512.939446123</v>
+        <v>8911446.443198577</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9794076.867678942</v>
+        <v>9792871.522703389</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10666223.66381564</v>
+        <v>10666492.81820894</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11547125.46565646</v>
+        <v>11548056.74644176</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12409305.34749728</v>
+        <v>12411317.81916258</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13271485.2293381</v>
+        <v>13274578.8918834</v>
       </c>
     </row>
   </sheetData>
@@ -26275,43 +26275,43 @@
         <v>1322345.892349224</v>
       </c>
       <c r="D2" t="n">
+        <v>1322345.892349225</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1322137.619257218</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1322137.619257218</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1322137.619257217</v>
+      </c>
+      <c r="M2" t="n">
         <v>1322345.892349224</v>
       </c>
-      <c r="E2" t="n">
-        <v>1322345.892349225</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="N2" t="n">
         <v>1322345.892349224</v>
       </c>
-      <c r="G2" t="n">
-        <v>1322345.892349224</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1322345.892349224</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1322345.892349224</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1322345.892349224</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1322345.892349225</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1322345.892349225</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1321352.702761222</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1321352.702761221</v>
-      </c>
       <c r="O2" t="n">
-        <v>1293269.822761222</v>
+        <v>1294891.609081217</v>
       </c>
       <c r="P2" t="n">
-        <v>1293269.822761222</v>
+        <v>1294891.609081217</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>232073.0000000002</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>594424.9999999998</v>
+        <v>594073</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>84320.00000000536</v>
+        <v>86080</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514545</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044576</v>
+        <v>599959.4017938485</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.404775654</v>
+        <v>597948.3132650447</v>
       </c>
       <c r="E4" t="n">
-        <v>513253.1653847606</v>
+        <v>513021.1273989228</v>
       </c>
       <c r="F4" t="n">
-        <v>511570.4197316588</v>
+        <v>511338.1266634626</v>
       </c>
       <c r="G4" t="n">
-        <v>509885.3519526902</v>
+        <v>509652.8034501313</v>
       </c>
       <c r="H4" t="n">
-        <v>508197.9453958012</v>
+        <v>507965.1411043515</v>
       </c>
       <c r="I4" t="n">
-        <v>506508.1831919707</v>
+        <v>506275.1227545453</v>
       </c>
       <c r="J4" t="n">
-        <v>504816.0482510949</v>
+        <v>504582.7313080163</v>
       </c>
       <c r="K4" t="n">
-        <v>503121.5232577762</v>
+        <v>502887.9494467443</v>
       </c>
       <c r="L4" t="n">
-        <v>501424.5906669989</v>
+        <v>501190.7596230533</v>
       </c>
       <c r="M4" t="n">
-        <v>505738.3237785171</v>
+        <v>505535.844925503</v>
       </c>
       <c r="N4" t="n">
-        <v>503972.1894956156</v>
+        <v>503772.9755574857</v>
       </c>
       <c r="O4" t="n">
-        <v>487738.9374419121</v>
+        <v>487867.9540901374</v>
       </c>
       <c r="P4" t="n">
-        <v>486030.0621167503</v>
+        <v>486160.9521894817</v>
       </c>
     </row>
     <row r="5">
@@ -26425,49 +26425,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58612.20000000003</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58612.20000000003</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58612.20000000003</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="F5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="G5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="H5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="I5" t="n">
-        <v>74075.349</v>
+        <v>74014.549</v>
       </c>
       <c r="J5" t="n">
-        <v>74075.34899999997</v>
+        <v>74014.549</v>
       </c>
       <c r="K5" t="n">
-        <v>74075.34899999997</v>
+        <v>74014.549</v>
       </c>
       <c r="L5" t="n">
-        <v>74075.34899999997</v>
+        <v>74014.549</v>
       </c>
       <c r="M5" t="n">
-        <v>70621.00500000094</v>
+        <v>70925.005</v>
       </c>
       <c r="N5" t="n">
-        <v>70621.00500000094</v>
+        <v>70925.005</v>
       </c>
       <c r="O5" t="n">
-        <v>68603.34900000093</v>
+        <v>68907.349</v>
       </c>
       <c r="P5" t="n">
-        <v>68603.34900000093</v>
+        <v>68907.349</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>429493.83498716</v>
+        <v>429692.9264977698</v>
       </c>
       <c r="C6" t="n">
-        <v>663575.1990447664</v>
+        <v>663774.2905553759</v>
       </c>
       <c r="D6" t="n">
-        <v>665586.28757357</v>
+        <v>665785.3790841799</v>
       </c>
       <c r="E6" t="n">
-        <v>140592.3779644644</v>
+        <v>141028.9428582942</v>
       </c>
       <c r="F6" t="n">
-        <v>736700.1236175653</v>
+        <v>736784.9435937544</v>
       </c>
       <c r="G6" t="n">
-        <v>738385.1913965341</v>
+        <v>738470.266807086</v>
       </c>
       <c r="H6" t="n">
-        <v>740072.597953423</v>
+        <v>740157.9291528658</v>
       </c>
       <c r="I6" t="n">
-        <v>741762.3601572533</v>
+        <v>741847.9475026731</v>
       </c>
       <c r="J6" t="n">
-        <v>355006.4950981294</v>
+        <v>355092.3389492009</v>
       </c>
       <c r="K6" t="n">
-        <v>745149.0200914489</v>
+        <v>745235.1208104732</v>
       </c>
       <c r="L6" t="n">
-        <v>746845.9526822262</v>
+        <v>746932.310634164</v>
       </c>
       <c r="M6" t="n">
-        <v>660673.3739826985</v>
+        <v>659805.0424237213</v>
       </c>
       <c r="N6" t="n">
-        <v>746759.5082656048</v>
+        <v>747647.9117917379</v>
       </c>
       <c r="O6" t="n">
-        <v>499327.5363193094</v>
+        <v>500516.3059910799</v>
       </c>
       <c r="P6" t="n">
-        <v>738636.411644471</v>
+        <v>739823.3078917356</v>
       </c>
     </row>
   </sheetData>
@@ -26859,49 +26859,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374.0000000000005</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>374.0000000000006</v>
+        <v>374</v>
       </c>
       <c r="D4" t="n">
-        <v>374.0000000000006</v>
+        <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J4" t="n">
-        <v>648.9999999999995</v>
+        <v>648</v>
       </c>
       <c r="K4" t="n">
-        <v>648.9999999999995</v>
+        <v>648</v>
       </c>
       <c r="L4" t="n">
-        <v>648.9999999999995</v>
+        <v>648</v>
       </c>
       <c r="M4" t="n">
-        <v>559.0000000000153</v>
+        <v>564</v>
       </c>
       <c r="N4" t="n">
-        <v>559.0000000000153</v>
+        <v>564</v>
       </c>
       <c r="O4" t="n">
-        <v>559.0000000000153</v>
+        <v>564</v>
       </c>
       <c r="P4" t="n">
-        <v>559.0000000000153</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -26999,16 +26999,16 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>297</v>
@@ -27085,19 +27085,19 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
         <v>374</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>185.0000000000081</v>
+        <v>190</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374.0000000000005</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>274.9999999999994</v>
+        <v>274</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857107</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>398.0465935392067</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,13 +27518,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.517988705216</v>
@@ -27533,7 +27533,7 @@
         <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>391.1981108900205</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27575,13 +27575,13 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>298.5879006898112</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>45.86273944538704</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613383</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C4" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
         <v>400</v>
-      </c>
-      <c r="C4" t="n">
-        <v>400</v>
-      </c>
-      <c r="D4" t="n">
-        <v>400</v>
-      </c>
-      <c r="E4" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.858135136612</v>
+        <v>350.4885601760532</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>314.4822279761349</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.13729309820286</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K4" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27651,16 +27651,16 @@
         <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.0465935392064</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>134.1177124465037</v>
@@ -27721,7 +27721,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,22 +27749,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632658</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>203.2450391696369</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>330.0284079411381</v>
@@ -27797,10 +27797,10 @@
         <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>217.2688067615395</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.44885845517678</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>58.37314290982795</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27846,10 +27846,10 @@
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.047816275856</v>
+        <v>174.2860247412752</v>
       </c>
       <c r="J7" t="n">
         <v>22.13729309820286</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>359.1365780635112</v>
+      </c>
+      <c r="T7" t="n">
+        <v>209.2309599488807</v>
+      </c>
+      <c r="U7" t="n">
+        <v>150.9482601269169</v>
+      </c>
+      <c r="V7" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W7" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>400</v>
-      </c>
-      <c r="U7" t="n">
-        <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>220.7881124996888</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X7" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.1643059857112</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>67.4463279765576</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>292.2280686811576</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86273944538698</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613378</v>
+        <v>25.39139276613437</v>
       </c>
     </row>
     <row r="10">
@@ -28068,22 +28068,22 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D10" t="n">
         <v>400</v>
       </c>
-      <c r="D10" t="n">
-        <v>293.0103176679686</v>
-      </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
@@ -28095,7 +28095,7 @@
         <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28122,7 +28122,7 @@
         <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>346.645127973855</v>
       </c>
     </row>
     <row r="11">
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28232,19 +28232,19 @@
         <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>319.4798568942807</v>
       </c>
       <c r="S12" t="n">
-        <v>205.2544342066189</v>
+        <v>321</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28286,10 +28286,10 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28356,10 +28356,10 @@
         <v>321</v>
       </c>
       <c r="T13" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="U13" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="V13" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>94.44753714149138</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28466,22 +28466,22 @@
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>128.2732823236868</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28508,10 +28508,10 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>321</v>
+        <v>319.4798568942806</v>
       </c>
       <c r="T15" t="n">
         <v>321</v>
@@ -28593,7 +28593,7 @@
         <v>321</v>
       </c>
       <c r="T16" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="U16" t="n">
         <v>321</v>
@@ -28605,7 +28605,7 @@
         <v>321</v>
       </c>
       <c r="X16" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="Y16" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>94.44753714149138</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28703,10 +28703,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>128.2732823236873</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
@@ -28766,7 +28766,7 @@
         <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>128.2732823236868</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28803,7 +28803,7 @@
         <v>321</v>
       </c>
       <c r="K19" t="n">
-        <v>321</v>
+        <v>309.7843364833207</v>
       </c>
       <c r="L19" t="n">
         <v>321</v>
@@ -28830,7 +28830,7 @@
         <v>321</v>
       </c>
       <c r="T19" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="U19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>161.1050265383575</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28940,13 +28940,13 @@
         <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28991,16 +28991,16 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>321</v>
+        <v>128.2732823236871</v>
       </c>
       <c r="V21" t="n">
-        <v>128.2732823236869</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>321</v>
@@ -29016,7 +29016,7 @@
         <v>321</v>
       </c>
       <c r="C22" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="D22" t="n">
         <v>321</v>
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>94.44753714149138</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>162.4939254614603</v>
+        <v>162.4939254614752</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29180,13 +29180,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>205.2544342066192</v>
+        <v>321</v>
       </c>
       <c r="H24" t="n">
         <v>321</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29234,13 +29234,13 @@
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>128.2732823236872</v>
       </c>
       <c r="X24" t="n">
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>321</v>
+      </c>
+      <c r="C25" t="n">
         <v>309.7843364833204</v>
-      </c>
-      <c r="C25" t="n">
-        <v>321</v>
       </c>
       <c r="D25" t="n">
         <v>321</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>161.1050265383594</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29417,16 +29417,16 @@
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>205.2544342066196</v>
+        <v>128.2732823236873</v>
       </c>
       <c r="I27" t="n">
         <v>191.2065745705938</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29471,13 +29471,13 @@
         <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29502,7 +29502,7 @@
         <v>321</v>
       </c>
       <c r="G28" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="H28" t="n">
         <v>321</v>
@@ -29547,7 +29547,7 @@
         <v>321</v>
       </c>
       <c r="V28" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
       <c r="W28" t="n">
         <v>321</v>
@@ -29617,7 +29617,7 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S29" t="n">
-        <v>319.6111010768992</v>
+        <v>321</v>
       </c>
       <c r="T29" t="n">
         <v>321</v>
@@ -29645,16 +29645,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>128.2732823236871</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -29663,7 +29663,7 @@
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>205.2544342066191</v>
       </c>
       <c r="I30" t="n">
         <v>191.2065745705938</v>
@@ -29690,13 +29690,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
       </c>
       <c r="S30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>321</v>
@@ -29711,7 +29711,7 @@
         <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29751,7 +29751,7 @@
         <v>321</v>
       </c>
       <c r="K31" t="n">
-        <v>321</v>
+        <v>309.7843364833207</v>
       </c>
       <c r="L31" t="n">
         <v>321</v>
@@ -29790,7 +29790,7 @@
         <v>321</v>
       </c>
       <c r="X31" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="Y31" t="n">
         <v>321</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>161.1050265383594</v>
+        <v>162.4939254614603</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29888,7 +29888,7 @@
         <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>321</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29939,7 +29939,7 @@
         <v>321</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>128.2732823236873</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -29948,7 +29948,7 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.2544342066195</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -30018,7 +30018,7 @@
         <v>321</v>
       </c>
       <c r="U34" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="V34" t="n">
         <v>321</v>
@@ -30027,7 +30027,7 @@
         <v>321</v>
       </c>
       <c r="X34" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="Y34" t="n">
         <v>321</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>162.4939254614603</v>
+        <v>154.9730265383577</v>
       </c>
       <c r="S35" t="n">
         <v>345</v>
@@ -30119,22 +30119,22 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
         <v>345</v>
       </c>
-      <c r="C36" t="n">
-        <v>325.2380554019696</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>324.9867056863481</v>
       </c>
       <c r="H36" t="n">
         <v>324.89733246944</v>
@@ -30176,7 +30176,7 @@
         <v>345</v>
       </c>
       <c r="U36" t="n">
-        <v>345</v>
+        <v>331.7341537129541</v>
       </c>
       <c r="V36" t="n">
         <v>345</v>
@@ -30188,7 +30188,7 @@
         <v>345</v>
       </c>
       <c r="Y36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30198,13 +30198,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>345</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E37" t="n">
         <v>345</v>
@@ -30213,16 +30213,16 @@
         <v>345</v>
       </c>
       <c r="G37" t="n">
-        <v>345</v>
+        <v>244.4127253005464</v>
       </c>
       <c r="H37" t="n">
-        <v>345</v>
+        <v>223.1596506917826</v>
       </c>
       <c r="I37" t="n">
         <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>345</v>
+        <v>317.2762142872849</v>
       </c>
       <c r="K37" t="n">
         <v>215.192904948684</v>
@@ -30255,10 +30255,10 @@
         <v>207.3278451947823</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9239650449497</v>
+        <v>345</v>
       </c>
       <c r="V37" t="n">
-        <v>290.5022075161868</v>
+        <v>345</v>
       </c>
       <c r="W37" t="n">
         <v>345</v>
@@ -30298,7 +30298,7 @@
         <v>345</v>
       </c>
       <c r="I38" t="n">
-        <v>95.83643606459415</v>
+        <v>88.31553714149135</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30401,13 +30401,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2513497156220268</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>345</v>
       </c>
       <c r="S39" t="n">
-        <v>345</v>
+        <v>326.3703960508307</v>
       </c>
       <c r="T39" t="n">
         <v>345</v>
@@ -30459,7 +30459,7 @@
         <v>345</v>
       </c>
       <c r="J40" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>345</v>
@@ -30489,22 +30489,22 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>310.2856121584461</v>
+        <v>345</v>
       </c>
       <c r="U40" t="n">
-        <v>150.9239650449497</v>
+        <v>156.7309898389671</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
-        <v>247.4436454301076</v>
+        <v>345</v>
       </c>
       <c r="Y40" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30593,10 +30593,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
@@ -30605,13 +30605,13 @@
         <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>205.2544342066192</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I42" t="n">
         <v>191.2065745705938</v>
@@ -30650,10 +30650,10 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>224.135387871417</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
         <v>321</v>
@@ -30672,7 +30672,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>321</v>
+        <v>309.7843364833207</v>
       </c>
       <c r="C43" t="n">
         <v>321</v>
@@ -30699,7 +30699,7 @@
         <v>321</v>
       </c>
       <c r="K43" t="n">
-        <v>309.7843364833207</v>
+        <v>321</v>
       </c>
       <c r="L43" t="n">
         <v>321</v>
@@ -30836,19 +30836,19 @@
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>224.13538787141</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>205.2544342066192</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>191.2065745705938</v>
@@ -30890,7 +30890,7 @@
         <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -30921,55 +30921,55 @@
         <v>321</v>
       </c>
       <c r="F46" t="n">
+        <v>321</v>
+      </c>
+      <c r="G46" t="n">
+        <v>321</v>
+      </c>
+      <c r="H46" t="n">
+        <v>321</v>
+      </c>
+      <c r="I46" t="n">
+        <v>321</v>
+      </c>
+      <c r="J46" t="n">
+        <v>321</v>
+      </c>
+      <c r="K46" t="n">
+        <v>321</v>
+      </c>
+      <c r="L46" t="n">
+        <v>321</v>
+      </c>
+      <c r="M46" t="n">
+        <v>321</v>
+      </c>
+      <c r="N46" t="n">
+        <v>321</v>
+      </c>
+      <c r="O46" t="n">
+        <v>321</v>
+      </c>
+      <c r="P46" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>321</v>
+      </c>
+      <c r="R46" t="n">
+        <v>321</v>
+      </c>
+      <c r="S46" t="n">
+        <v>321</v>
+      </c>
+      <c r="T46" t="n">
+        <v>321</v>
+      </c>
+      <c r="U46" t="n">
+        <v>321</v>
+      </c>
+      <c r="V46" t="n">
         <v>309.7843364833204</v>
-      </c>
-      <c r="G46" t="n">
-        <v>321</v>
-      </c>
-      <c r="H46" t="n">
-        <v>321</v>
-      </c>
-      <c r="I46" t="n">
-        <v>321</v>
-      </c>
-      <c r="J46" t="n">
-        <v>321</v>
-      </c>
-      <c r="K46" t="n">
-        <v>321</v>
-      </c>
-      <c r="L46" t="n">
-        <v>321</v>
-      </c>
-      <c r="M46" t="n">
-        <v>321</v>
-      </c>
-      <c r="N46" t="n">
-        <v>321</v>
-      </c>
-      <c r="O46" t="n">
-        <v>321</v>
-      </c>
-      <c r="P46" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>321</v>
-      </c>
-      <c r="R46" t="n">
-        <v>321</v>
-      </c>
-      <c r="S46" t="n">
-        <v>321</v>
-      </c>
-      <c r="T46" t="n">
-        <v>321</v>
-      </c>
-      <c r="U46" t="n">
-        <v>321</v>
-      </c>
-      <c r="V46" t="n">
-        <v>321</v>
       </c>
       <c r="W46" t="n">
         <v>321</v>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>181.617406216003</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
         <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517586</v>
+        <v>246.8601159786807</v>
       </c>
       <c r="M2" t="n">
-        <v>374.0000000000005</v>
+        <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>374.0000000000005</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374.0000000000005</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>105.6304250394411</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>143.434411700279</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34937,16 +34937,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>374.0000000000006</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
-        <v>374.0000000000006</v>
+        <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517591</v>
+        <v>374</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>234.2887077235405</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>374.0000000000006</v>
+        <v>299.5314174862185</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35132,10 +35132,10 @@
         <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3.238208465419267</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.86342193648883</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>21.61780228347257</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517586</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M8" t="n">
-        <v>374.0000000000006</v>
+        <v>234.2887077235401</v>
       </c>
       <c r="N8" t="n">
-        <v>374.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>181.5167089435052</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>374.0000000000006</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35305,7 +35305,7 @@
         <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>143.085042164504</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
         <v>192.2472765237492</v>
@@ -35354,22 +35354,22 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>7.474099612413095</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>228.952183724144</v>
@@ -35381,7 +35381,7 @@
         <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,7 +35408,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>59.17977512439269</v>
       </c>
     </row>
     <row r="11">
@@ -35457,16 +35457,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K11" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L11" t="n">
-        <v>649.0000000000001</v>
+        <v>647.9999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>169.5323468034707</v>
+        <v>648.000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>168.5727508438742</v>
       </c>
       <c r="O11" t="n">
         <v>166.8217284158573</v>
@@ -35603,10 +35603,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H13" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I13" t="n">
         <v>163.3468722487342</v>
@@ -35642,10 +35642,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>102.456491288538</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U13" t="n">
-        <v>170.0760349550503</v>
+        <v>158.8603714383707</v>
       </c>
       <c r="V13" t="n">
         <v>121.8296897837838</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K14" t="n">
-        <v>178.9801507537688</v>
+        <v>648</v>
       </c>
       <c r="L14" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M14" t="n">
-        <v>41.23339715462306</v>
+        <v>648.0000000000015</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>594.5320473262855</v>
       </c>
       <c r="O14" t="n">
         <v>166.8217284158573</v>
@@ -35712,7 +35712,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q14" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>113.6721548052177</v>
+        <v>102.4564912885381</v>
       </c>
       <c r="U16" t="n">
         <v>170.0760349550503</v>
@@ -35891,7 +35891,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X16" t="n">
-        <v>62.34069105321293</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y16" t="n">
         <v>33.53464715053764</v>
@@ -35937,19 +35937,19 @@
         <v>222.040703517588</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>648.0000000000015</v>
       </c>
       <c r="N17" t="n">
-        <v>471.5381337407799</v>
+        <v>136.4199820331172</v>
       </c>
       <c r="O17" t="n">
-        <v>166.8217284158573</v>
+        <v>648.0000000000015</v>
       </c>
       <c r="P17" t="n">
-        <v>202.0463570447457</v>
+        <v>648.0000000000015</v>
       </c>
       <c r="Q17" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36077,10 +36077,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>76.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H19" t="n">
-        <v>97.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I19" t="n">
         <v>163.3468722487342</v>
@@ -36089,7 +36089,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K19" t="n">
-        <v>105.807095051316</v>
+        <v>94.59143153463661</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>102.456491288538</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U19" t="n">
         <v>170.0760349550503</v>
@@ -36171,13 +36171,13 @@
         <v>178.9801507537688</v>
       </c>
       <c r="L20" t="n">
-        <v>222.040703517588</v>
+        <v>648</v>
       </c>
       <c r="M20" t="n">
-        <v>471.53813374078</v>
+        <v>648.0000000000033</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>42.61924129876854</v>
       </c>
       <c r="O20" t="n">
         <v>166.8217284158573</v>
@@ -36302,7 +36302,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C22" t="n">
-        <v>48.27475335195533</v>
+        <v>37.05908983527576</v>
       </c>
       <c r="D22" t="n">
         <v>35.46378194444452</v>
@@ -36323,7 +36323,7 @@
         <v>163.3468722487342</v>
       </c>
       <c r="J22" t="n">
-        <v>319.1375187949537</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K22" t="n">
         <v>105.807095051316</v>
@@ -36405,16 +36405,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K23" t="n">
-        <v>178.9801507537688</v>
+        <v>647.5586885349504</v>
       </c>
       <c r="L23" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M23" t="n">
-        <v>471.53813374078</v>
+        <v>648.0000000000024</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>166.8217284158573</v>
@@ -36536,10 +36536,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22.6705361462418</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>48.27475335195533</v>
+        <v>37.05908983527576</v>
       </c>
       <c r="D25" t="n">
         <v>35.46378194444452</v>
@@ -36642,22 +36642,22 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K26" t="n">
-        <v>178.9801507537689</v>
+        <v>648</v>
       </c>
       <c r="L26" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M26" t="n">
-        <v>137.3795779927169</v>
+        <v>594.5320473262869</v>
       </c>
       <c r="N26" t="n">
-        <v>648.9999999999995</v>
+        <v>648</v>
       </c>
       <c r="O26" t="n">
-        <v>648.9999999999995</v>
+        <v>166.8217284158573</v>
       </c>
       <c r="P26" t="n">
-        <v>648.9999999999995</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36788,10 +36788,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>76.58727469945357</v>
+        <v>65.371611182774</v>
       </c>
       <c r="H28" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I28" t="n">
         <v>163.3468722487342</v>
@@ -36833,7 +36833,7 @@
         <v>170.0760349550503</v>
       </c>
       <c r="V28" t="n">
-        <v>110.6140262671042</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W28" t="n">
         <v>94.62719016129032</v>
@@ -36879,16 +36879,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K29" t="n">
-        <v>178.9801507537689</v>
+        <v>648</v>
       </c>
       <c r="L29" t="n">
-        <v>222.040703517588</v>
+        <v>647.9999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>648.9999999999995</v>
+        <v>168.5727508438752</v>
       </c>
       <c r="N29" t="n">
-        <v>471.5381337407785</v>
+        <v>648</v>
       </c>
       <c r="O29" t="n">
         <v>166.8217284158573</v>
@@ -36897,7 +36897,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q29" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K31" t="n">
-        <v>105.807095051316</v>
+        <v>94.59143153463661</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37076,7 +37076,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X31" t="n">
-        <v>62.34069105321293</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y31" t="n">
         <v>33.53464715053764</v>
@@ -37116,16 +37116,16 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K32" t="n">
-        <v>178.9801507537689</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L32" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M32" t="n">
-        <v>471.5381337407786</v>
+        <v>648</v>
       </c>
       <c r="N32" t="n">
-        <v>648.9999999999995</v>
+        <v>468.5785377811841</v>
       </c>
       <c r="O32" t="n">
         <v>166.8217284158573</v>
@@ -37262,10 +37262,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G34" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H34" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I34" t="n">
         <v>163.3468722487342</v>
@@ -37304,7 +37304,7 @@
         <v>113.6721548052177</v>
       </c>
       <c r="U34" t="n">
-        <v>170.0760349550503</v>
+        <v>158.8603714383707</v>
       </c>
       <c r="V34" t="n">
         <v>121.8296897837838</v>
@@ -37313,7 +37313,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>62.34069105321293</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
         <v>33.53464715053764</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K35" t="n">
-        <v>178.9801507537689</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L35" t="n">
-        <v>222.040703517588</v>
+        <v>564</v>
       </c>
       <c r="M35" t="n">
-        <v>559.0000000000053</v>
+        <v>564</v>
       </c>
       <c r="N35" t="n">
-        <v>241.1478561685278</v>
+        <v>42.68180289788913</v>
       </c>
       <c r="O35" t="n">
         <v>166.8217284158573</v>
@@ -37371,7 +37371,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q35" t="n">
-        <v>559.0000000000053</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,7 +37435,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L36" t="n">
-        <v>418.2869675055536</v>
+        <v>437.5512810090644</v>
       </c>
       <c r="M36" t="n">
         <v>277.7000421645042</v>
@@ -37484,13 +37484,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
         <v>64.01909516304346</v>
@@ -37499,16 +37499,16 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>100.5872746994536</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>121.8403493082175</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>187.3468722487342</v>
       </c>
       <c r="J37" t="n">
-        <v>354.3531823116332</v>
+        <v>326.6293965989182</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -37541,10 +37541,10 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>194.0760349550503</v>
       </c>
       <c r="V37" t="n">
-        <v>91.33189729997063</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W37" t="n">
         <v>118.6271901612903</v>
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K38" t="n">
-        <v>548.8232703361474</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L38" t="n">
-        <v>222.0407035175879</v>
+        <v>564</v>
       </c>
       <c r="M38" t="n">
-        <v>559.0000000000035</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>472.9865394840456</v>
       </c>
       <c r="O38" t="n">
         <v>166.8217284158573</v>
@@ -37608,7 +37608,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37678,7 +37678,7 @@
         <v>277.7000421645042</v>
       </c>
       <c r="N39" t="n">
-        <v>311.1608215108046</v>
+        <v>330.4251350143152</v>
       </c>
       <c r="O39" t="n">
         <v>420.5744747329351</v>
@@ -37745,7 +37745,7 @@
         <v>187.3468722487342</v>
       </c>
       <c r="J40" t="n">
-        <v>354.3531823116332</v>
+        <v>9.353182311633219</v>
       </c>
       <c r="K40" t="n">
         <v>129.807095051316</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>102.9577669636638</v>
+        <v>137.6721548052177</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>5.807024794017331</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37827,22 +37827,22 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K41" t="n">
-        <v>559.0000000000153</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L41" t="n">
-        <v>222.040703517588</v>
+        <v>472.9865394840458</v>
       </c>
       <c r="M41" t="n">
-        <v>559.0000000000053</v>
+        <v>564</v>
       </c>
       <c r="N41" t="n">
-        <v>63.17436396702738</v>
+        <v>564</v>
       </c>
       <c r="O41" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P41" t="n">
-        <v>559.0000000000053</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L42" t="n">
-        <v>418.2869675055463</v>
+        <v>437.5512810090644</v>
       </c>
       <c r="M42" t="n">
         <v>277.7000421645042</v>
@@ -37958,7 +37958,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33.88619966292134</v>
+        <v>22.67053614624203</v>
       </c>
       <c r="C43" t="n">
         <v>48.27475335195533</v>
@@ -37985,7 +37985,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K43" t="n">
-        <v>94.59143153463661</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38064,25 +38064,25 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K44" t="n">
-        <v>178.9801507537689</v>
+        <v>564</v>
       </c>
       <c r="L44" t="n">
         <v>222.040703517588</v>
       </c>
       <c r="M44" t="n">
-        <v>559.0000000000072</v>
+        <v>67.97234376497215</v>
       </c>
       <c r="N44" t="n">
-        <v>241.1478561685242</v>
+        <v>564</v>
       </c>
       <c r="O44" t="n">
         <v>166.8217284158573</v>
       </c>
       <c r="P44" t="n">
-        <v>202.0463570447457</v>
+        <v>564</v>
       </c>
       <c r="Q44" t="n">
-        <v>559.0000000000072</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,7 +38146,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L45" t="n">
-        <v>418.2869675055536</v>
+        <v>437.5512810090644</v>
       </c>
       <c r="M45" t="n">
         <v>277.7000421645042</v>
@@ -38207,7 +38207,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>35.40148051557846</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G46" t="n">
         <v>76.58727469945359</v>
@@ -38255,7 +38255,7 @@
         <v>170.0760349550503</v>
       </c>
       <c r="V46" t="n">
-        <v>121.8296897837838</v>
+        <v>110.6140262671042</v>
       </c>
       <c r="W46" t="n">
         <v>94.62719016129032</v>
